--- a/homes.xlsx
+++ b/homes.xlsx
@@ -425,68 +425,3006 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:J68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>address</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>address</t>
+          <t>city</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>state</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>state</t>
+          <t>zip</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>zip</t>
+          <t>price</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>price</t>
+          <t>beds</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>beds</t>
+          <t>baths</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>baths</t>
+          <t>sqft</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>sqft</t>
+          <t>url</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>url</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>image</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
           <t>date_seen</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>378 Willow St</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Elko</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>89801.0</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>308000</v>
+      </c>
+      <c r="F2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1345</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>https://www.redfin.com/NV/Elko/378-Willow-St-89801/home/136521609</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>671 Ouderkirk Ave</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Elko</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>89801.0</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>300000</v>
+      </c>
+      <c r="F3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1568</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>https://www.redfin.com/NV/Elko/671-Ouderkirk-St-89801/home/136271755</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>391 Edgebrook Dr</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Spring Creek</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>89815.0</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>449000</v>
+      </c>
+      <c r="F4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2247</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>https://www.redfin.com/NV/Spring-Creek/391-Edgebrook-Dr-89815/home/136354964</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2623 Platinum Dr</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Elko</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>89801.0</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>459900</v>
+      </c>
+      <c r="F5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2145</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>https://www.redfin.com/NV/Elko/2623-Platinum-Dr-89801/home/197678072</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2210 Clearwater Ct</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Elko</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>89801.0</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>405000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2094</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>https://www.redfin.com/NV/Elko/2210-Clearwater-Ct-89801/home/136399185</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>458 Lawndale Dr</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Spring Creek</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>89815.0</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>458000</v>
+      </c>
+      <c r="F7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1864</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>https://www.redfin.com/NV/Spring-Creek/458-Lawndale-Dr-89815/home/136539743</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2531 N 5th St</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Elko</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>89801.0</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>369900</v>
+      </c>
+      <c r="F8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1647</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>https://www.redfin.com/NV/Elko/2531-N-5th-St-89801/home/197678096</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>575 12th St</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Elko</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>89801.0</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>365000</v>
+      </c>
+      <c r="F9" t="n">
+        <v>4</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>https://www.redfin.com/NV/Elko/575-12th-St-89801/home/136240270</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>3514 Hawthorne Dr</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Elko</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>89801.0</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>445000</v>
+      </c>
+      <c r="F10" t="n">
+        <v>5</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2579</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>https://www.redfin.com/NV/Elko/3514-Hawthorne-Dr-89801/home/136387668</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>530 Shadybrook Dr</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Spring Creek</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>89801.0</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>550000</v>
+      </c>
+      <c r="F11" t="n">
+        <v>3</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1824</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>https://www.redfin.com/NV/Spring-Creek/530-Shadybrook-Dr-89815/home/136314059</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>618 Tasha Way</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Elko</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>89801.0</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>414000</v>
+      </c>
+      <c r="F12" t="n">
+        <v>4</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1859</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>https://www.redfin.com/NV/Elko/618-Tasha-Way-89801/home/147077949</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>13 Lawndale Ct</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Spring Creek</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>89815.0</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>350000</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1144</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>https://www.redfin.com/NV/Spring-Creek/13-Lawndale-Ct-89815/home/136385594</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>534 Spring Creek Pkwy</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Spring Creek</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>89815.0</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>492000</v>
+      </c>
+      <c r="F14" t="n">
+        <v>4</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2134</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>https://www.redfin.com/NV/Spring-Creek/534-Spring-Creek-Pkwy-89815/home/136428220</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>301 Onyx Way St</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>West Wendover</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>89883.0</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>595000</v>
+      </c>
+      <c r="F15" t="n">
+        <v>3</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H15" t="n">
+        <v>4106</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>https://www.redfin.com/NV/West-Wendover/301-Onyx-Way-89835/home/204646573</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2126 Colonial Dr</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Elko</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>89801.0</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>415000</v>
+      </c>
+      <c r="F16" t="n">
+        <v>4</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2136</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>https://www.redfin.com/NV/Elko/2126-Colonial-Dr-89801/home/136514237</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>144 Charlwood Pl</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Spring Creek</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>89815.0</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>350000</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1370</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>https://www.redfin.com/NV/Spring-Creek/144-Charlwood-Pl-89815/home/136264242</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>5736 Platte Ave</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Elko</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>89801.0</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>420000</v>
+      </c>
+      <c r="F18" t="n">
+        <v>3</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1541</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>https://www.redfin.com/NV/Elko/5736-Platte-AVE-89801/home/204514170</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1933 Pheasant Dr</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Elko</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>89801.0</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>570000</v>
+      </c>
+      <c r="F19" t="n">
+        <v>3</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2220</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>https://www.redfin.com/NV/Elko/1933-Pheasant-Dr-89801/home/177198540</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>4005 Louise Ln</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Elko</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>89801.0</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>530000</v>
+      </c>
+      <c r="F20" t="n">
+        <v>3</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>https://www.redfin.com/NV/Elko/4005-Louise-LN-89801/home/204349693</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>4003 Louise Ln</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Elko</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>89801.0</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>530000</v>
+      </c>
+      <c r="F21" t="n">
+        <v>3</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>https://www.redfin.com/NV/Elko/4003-Louise-LN-89801/home/204349692</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>4021 Coco Ct</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Elko</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>89801.0</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>530000</v>
+      </c>
+      <c r="F22" t="n">
+        <v>3</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>https://www.redfin.com/NV/Elko/4021-Connecticut-Pl-89801/home/204349599</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>4020 Louise Ln</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Elko</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>89801.0</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>530000</v>
+      </c>
+      <c r="F23" t="n">
+        <v>3</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>https://www.redfin.com/NV/Elko/4020-Louise-LN-89801/home/204349598</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>4012 Louise Ln</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Elko</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>89801.0</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>530000</v>
+      </c>
+      <c r="F24" t="n">
+        <v>3</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>https://www.redfin.com/NV/Elko/4012-Louise-LN-89801/home/204349573</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>4016 Louise Ln</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Elko</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>89801.0</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>530000</v>
+      </c>
+      <c r="F25" t="n">
+        <v>3</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>https://www.redfin.com/NV/Elko/4016-Louise-LN-89801/home/204349572</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>4018 Louise Ln</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Elko</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>89801.0</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>530000</v>
+      </c>
+      <c r="F26" t="n">
+        <v>3</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>https://www.redfin.com/NV/Elko/4018-Louise-LN-89801/home/204349571</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>4008 Louise Ln</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Elko</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>89801.0</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>530000</v>
+      </c>
+      <c r="F27" t="n">
+        <v>3</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>https://www.redfin.com/NV/Elko/4008-Louise-LN-89801/home/204349495</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>4010 Louise Ln</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Elko</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>89801.0</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>530000</v>
+      </c>
+      <c r="F28" t="n">
+        <v>3</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>https://www.redfin.com/NV/Elko/4010-Louise-LN-89801/home/204349490</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>4006 Louise Ln</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Elko</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>89801.0</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>530000</v>
+      </c>
+      <c r="F29" t="n">
+        <v>3</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>https://www.redfin.com/NV/Elko/4006-Louise-LN-89801/home/204349488</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>4004 Louise Ln</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Elko</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>89801.0</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>530000</v>
+      </c>
+      <c r="F30" t="n">
+        <v>3</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>https://www.redfin.com/NV/Elko/4004-Louise-LN-89801/home/204349371</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>841 Northside Dr</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Elko</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>89801.0</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>349000</v>
+      </c>
+      <c r="F31" t="n">
+        <v>4</v>
+      </c>
+      <c r="G31" t="n">
+        <v>2</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2304</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>https://www.redfin.com/NV/Elko/841-Northside-Dr-89801/home/136529082</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>697 Clover Dr</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Spring Creek</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>89815.0</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>389000</v>
+      </c>
+      <c r="F32" t="n">
+        <v>3</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1688</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>https://www.redfin.com/NV/Spring-Creek/697-Clover-Dr-89815/home/136258428</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>388 Fairway Blvd</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Spring Creek</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>89815.0</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>569900</v>
+      </c>
+      <c r="F33" t="n">
+        <v>5</v>
+      </c>
+      <c r="G33" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H33" t="n">
+        <v>3231</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>https://www.redfin.com/NV/Spring-Creek/388-Fairway-Blvd-89815/home/136270687</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>597 Shadybrook Dr</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Spring Creek</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>89815.0</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>395000</v>
+      </c>
+      <c r="F34" t="n">
+        <v>3</v>
+      </c>
+      <c r="G34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H34" t="n">
+        <v>2277</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>https://www.redfin.com/NV/Spring-Creek/597-Shadybrook-Dr-89815/home/136202654</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>739 Wolcott Dr</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Spring Creek</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>89815.0</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>399000</v>
+      </c>
+      <c r="F35" t="n">
+        <v>3</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1706</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>https://www.redfin.com/NV/Spring-Creek/739-Wolcott-Dr-89815/home/136232546</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>3145 Newcastle Cir</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Elko</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>89801.0</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>580000</v>
+      </c>
+      <c r="F36" t="n">
+        <v>5</v>
+      </c>
+      <c r="G36" t="n">
+        <v>3</v>
+      </c>
+      <c r="H36" t="n">
+        <v>2627</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>https://www.redfin.com/NV/Elko/3145-Newcastle-Cir-89801/home/181896216</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>228 Lawndale Dr</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Spring Creek</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>89815.0</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>365000</v>
+      </c>
+      <c r="F37" t="n">
+        <v>3</v>
+      </c>
+      <c r="G37" t="n">
+        <v>2</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1392</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>https://www.redfin.com/NV/Spring-Creek/228-Lawndale-Dr-89815/home/136345151</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>389 Lakeport Bay</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Spring Creek</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>89815.0</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>385000</v>
+      </c>
+      <c r="F38" t="n">
+        <v>4</v>
+      </c>
+      <c r="G38" t="n">
+        <v>3</v>
+      </c>
+      <c r="H38" t="n">
+        <v>2192</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>https://www.redfin.com/NV/Spring-Creek/389-Lakeport-Bay-89815/home/136492739</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>5743 Kale Dr</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Elko</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>89801.0</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>394900</v>
+      </c>
+      <c r="F39" t="n">
+        <v>3</v>
+      </c>
+      <c r="G39" t="n">
+        <v>2</v>
+      </c>
+      <c r="H39" t="n">
+        <v>2715</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>https://www.redfin.com/NV/Elko/5743-Kale-Dr-89801/home/136233320</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>191 Greencrest Pl</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Spring Creek</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>89815.0</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>499900</v>
+      </c>
+      <c r="F40" t="n">
+        <v>4</v>
+      </c>
+      <c r="G40" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H40" t="n">
+        <v>2597</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>https://www.redfin.com/NV/Spring-Creek/191-Greencrest-Pl-89815/home/136519054</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2110 Sierra Cir</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Elko</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>89801.0</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>560000</v>
+      </c>
+      <c r="F41" t="n">
+        <v>6</v>
+      </c>
+      <c r="G41" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H41" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>https://www.redfin.com/NV/Elko/2110-Sierra-Cir-89801/home/136496014</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>3129 Newcastle Cir</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Elko</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>89801.0</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>585000</v>
+      </c>
+      <c r="F42" t="n">
+        <v>4</v>
+      </c>
+      <c r="G42" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H42" t="n">
+        <v>2264</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>https://www.redfin.com/NV/Elko/3129-Newcastle-Cir-89801/home/181896211</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>175 Greencrest Dr</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Spring Creek</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>89815.0</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>380000</v>
+      </c>
+      <c r="F43" t="n">
+        <v>3</v>
+      </c>
+      <c r="G43" t="n">
+        <v>2</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1308</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>https://www.redfin.com/NV/Spring-Creek/175-Greencrest-Dr-89815/home/136535416</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2446 Khoury Ln</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Elko</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>89801.0</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>410000</v>
+      </c>
+      <c r="F44" t="n">
+        <v>4</v>
+      </c>
+      <c r="G44" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H44" t="n">
+        <v>2555</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>https://www.redfin.com/NV/Elko/2446-Khoury-Ln-89801/home/136664205</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>3555 Desert Plains Ave</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Elko</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>89801.0</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>369900</v>
+      </c>
+      <c r="F45" t="n">
+        <v>3</v>
+      </c>
+      <c r="G45" t="n">
+        <v>2</v>
+      </c>
+      <c r="H45" t="n">
+        <v>1989</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>https://www.redfin.com/NV/Elko/3555-Desert-Plains-Ave-89801/home/136360258</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>1112 Ruby Ave</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Wells</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>89835.0</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>279900</v>
+      </c>
+      <c r="F46" t="n">
+        <v>3</v>
+      </c>
+      <c r="G46" t="n">
+        <v>2</v>
+      </c>
+      <c r="H46" t="n">
+        <v>2986</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>https://www.redfin.com/NV/Wells/1112-Ruby-Ave-89835/home/136304365</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>202 Chris Ave</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Elko</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>89801.0</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>470000</v>
+      </c>
+      <c r="F47" t="n">
+        <v>4</v>
+      </c>
+      <c r="G47" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H47" t="n">
+        <v>2490</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>https://www.redfin.com/NV/Elko/202-Chris-Ave-89801/home/136272897</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2990 Eleanor Ct</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Elko</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>89801.0</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>589900</v>
+      </c>
+      <c r="F48" t="n">
+        <v>3</v>
+      </c>
+      <c r="G48" t="n">
+        <v>2</v>
+      </c>
+      <c r="H48" t="n">
+        <v>1929</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>https://www.redfin.com/NV/Elko/2990-Eleanor-Ct-89801/home/188083427</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>112 Agate Dr</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Spring Creek</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>89815.0</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>390000</v>
+      </c>
+      <c r="F49" t="n">
+        <v>4</v>
+      </c>
+      <c r="G49" t="n">
+        <v>2</v>
+      </c>
+      <c r="H49" t="n">
+        <v>1700</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>https://www.redfin.com/NV/Spring-Creek/112-Agate-Dr-89815/home/136481108</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>412 Edgebrook Way</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Spring Creek</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>89815.0</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>464000</v>
+      </c>
+      <c r="F50" t="n">
+        <v>5</v>
+      </c>
+      <c r="G50" t="n">
+        <v>2</v>
+      </c>
+      <c r="H50" t="n">
+        <v>2100</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>https://www.redfin.com/NV/Spring-Creek/412-Edgebrook-Way-89815/home/136433936</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>116 Court St</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Elko</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>89801.0</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>575000</v>
+      </c>
+      <c r="F51" t="n">
+        <v>5</v>
+      </c>
+      <c r="G51" t="n">
+        <v>3</v>
+      </c>
+      <c r="H51" t="n">
+        <v>3737</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>https://www.redfin.com/NV/Elko/116-Court-St-89801/home/136381837</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>459 S 9th St</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Elko</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>89801.0</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>410000</v>
+      </c>
+      <c r="F52" t="n">
+        <v>3</v>
+      </c>
+      <c r="G52" t="n">
+        <v>2</v>
+      </c>
+      <c r="H52" t="n">
+        <v>2467</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>https://www.redfin.com/NV/Elko/459-S-9th-St-89801/home/136446385</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>878 Abeyta Dr</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Spring Creek</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>89815.0</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>594000</v>
+      </c>
+      <c r="F53" t="n">
+        <v>6</v>
+      </c>
+      <c r="G53" t="n">
+        <v>3</v>
+      </c>
+      <c r="H53" t="n">
+        <v>3322</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>https://www.redfin.com/NV/Spring-Creek/878-Abeyta-Dr-89815/home/136647046</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2963 Eleanor Ct</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Elko</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>89801.0</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>489900</v>
+      </c>
+      <c r="F54" t="n">
+        <v>3</v>
+      </c>
+      <c r="G54" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H54" t="n">
+        <v>1619</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>https://www.redfin.com/NV/Elko/2963-Aria-Way-89801/home/196168718</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2939 Eleanor Ct</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Elko</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>89801.0</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>489900</v>
+      </c>
+      <c r="F55" t="n">
+        <v>3</v>
+      </c>
+      <c r="G55" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H55" t="n">
+        <v>1619</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>https://www.redfin.com/NV/Elko/2939-Aria-Way-89801/home/196168640</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>1262 Primrose Ln</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Elko</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>89801.0</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>458275</v>
+      </c>
+      <c r="F56" t="n">
+        <v>3</v>
+      </c>
+      <c r="G56" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H56" t="n">
+        <v>1619</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>https://www.redfin.com/NV/Elko/1262-Primrose-Ln-89801/home/200791027</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2943 Eleanor Ct</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Elko</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>89801.0</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>539900</v>
+      </c>
+      <c r="F57" t="n">
+        <v>4</v>
+      </c>
+      <c r="G57" t="n">
+        <v>2</v>
+      </c>
+      <c r="H57" t="n">
+        <v>1938</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>https://www.redfin.com/NV/Elko/2943-Eleanor-Ct-89801/home/188083456</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2953 Eleanor Ct</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Elko</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>89801.0</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>536900</v>
+      </c>
+      <c r="F58" t="n">
+        <v>4</v>
+      </c>
+      <c r="G58" t="n">
+        <v>2</v>
+      </c>
+      <c r="H58" t="n">
+        <v>1938</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>https://www.redfin.com/NV/Elko/2953-Eleanor-Ct-89801/home/188083454</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2918 Aria Way</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Elko</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>89801.0</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>489900</v>
+      </c>
+      <c r="F59" t="n">
+        <v>3</v>
+      </c>
+      <c r="G59" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H59" t="n">
+        <v>1619</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>https://www.redfin.com/NV/Elko/2918-Aria-Way-89801/home/197554256</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>1287 Primrose Ln</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Elko</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>89801.0</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>409000</v>
+      </c>
+      <c r="F60" t="n">
+        <v>3</v>
+      </c>
+      <c r="G60" t="n">
+        <v>2</v>
+      </c>
+      <c r="H60" t="n">
+        <v>1410</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>https://www.redfin.com/NV/Elko/1287-Primrose-Ln-89801/home/200522444</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2432 Khoury Ln</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Elko</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>89801.0</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>399000</v>
+      </c>
+      <c r="F61" t="n">
+        <v>3</v>
+      </c>
+      <c r="G61" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H61" t="n">
+        <v>2245</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>https://www.redfin.com/NV/Elko/2432-Khoury-Ln-89801/home/136664172</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>1723 Opal Dr</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Elko</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>89801.0</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>469000</v>
+      </c>
+      <c r="F62" t="n">
+        <v>3</v>
+      </c>
+      <c r="G62" t="n">
+        <v>2</v>
+      </c>
+      <c r="H62" t="n">
+        <v>1770</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>https://www.redfin.com/NV/Elko/1723-Opal-Dr-89801/home/177198452</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>4434 York Blvd #62</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Elko</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>89801.0</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>501000</v>
+      </c>
+      <c r="F63" t="n">
+        <v>4</v>
+      </c>
+      <c r="G63" t="n">
+        <v>2</v>
+      </c>
+      <c r="H63" t="n">
+        <v>1660</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>https://www.redfin.com/NV/Elko/4434-York-BLVD-89801/unit-62/home/200801805</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>773 Juniper St</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Elko</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>89801.0</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>249999</v>
+      </c>
+      <c r="F64" t="n">
+        <v>4</v>
+      </c>
+      <c r="G64" t="n">
+        <v>1</v>
+      </c>
+      <c r="H64" t="n">
+        <v>2899</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>https://www.redfin.com/NV/Elko/773-Juniper-St-89801/home/136481949</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>268 5th St</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Elko</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>89835.0</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>230000</v>
+      </c>
+      <c r="F65" t="n">
+        <v>4</v>
+      </c>
+      <c r="G65" t="n">
+        <v>1</v>
+      </c>
+      <c r="H65" t="n">
+        <v>1907</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>https://www.redfin.com/NV/Elko/268-5th-St-89801/home/136211989</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2279 Gurley Dr</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Jackpot</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>89825.0</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>319900</v>
+      </c>
+      <c r="F66" t="n">
+        <v>3</v>
+      </c>
+      <c r="G66" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H66" t="n">
+        <v>1152</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>https://www.redfin.com/NV/Jackpot/2279-Gurley-Dr-89825/home/136242555</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>629 Palace Pkwy</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Spring Creek</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>89815.0</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>399000</v>
+      </c>
+      <c r="F67" t="n">
+        <v>4</v>
+      </c>
+      <c r="G67" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H67" t="n">
+        <v>1953</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>https://www.redfin.com/NV/Spring-Creek/629-Palace-Pkwy-89815/home/136541966</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>710 Cedar St</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Elko</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>89822.0</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>200000</v>
+      </c>
+      <c r="F68" t="n">
+        <v>4</v>
+      </c>
+      <c r="G68" t="n">
+        <v>4</v>
+      </c>
+      <c r="H68" t="n">
+        <v>1608</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>https://www.redfin.com/NV/Elko/710-Cedar-St-89801/home/136478460</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>

--- a/homes.xlsx
+++ b/homes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V136"/>
+  <dimension ref="A1:V137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -593,7 +593,7 @@
         <v>1962</v>
       </c>
       <c r="N2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O2" t="n">
         <v>235</v>
@@ -679,7 +679,7 @@
         <v>1966</v>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O3" t="n">
         <v>257</v>
@@ -765,7 +765,7 @@
         <v>1900</v>
       </c>
       <c r="N4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O4" t="n">
         <v>67</v>
@@ -851,7 +851,7 @@
         <v>1900</v>
       </c>
       <c r="N5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O5" t="n">
         <v>86</v>
@@ -937,7 +937,7 @@
         <v>1920</v>
       </c>
       <c r="N6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O6" t="n">
         <v>131</v>
@@ -1023,7 +1023,7 @@
         <v>1885</v>
       </c>
       <c r="N7" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O7" t="n">
         <v>124</v>
@@ -1109,7 +1109,7 @@
         <v>2017</v>
       </c>
       <c r="N8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O8" t="n">
         <v>166</v>
@@ -1197,7 +1197,7 @@
         <v>1924</v>
       </c>
       <c r="N9" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O9" t="n">
         <v>155</v>
@@ -1283,7 +1283,7 @@
         <v>1900</v>
       </c>
       <c r="N10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O10" t="n">
         <v>165</v>
@@ -1369,7 +1369,7 @@
         <v>1973</v>
       </c>
       <c r="N11" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O11" t="n">
         <v>184</v>
@@ -1457,7 +1457,7 @@
         <v>2005</v>
       </c>
       <c r="N12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O12" t="n">
         <v>172</v>
@@ -1543,7 +1543,7 @@
         <v>2015</v>
       </c>
       <c r="N13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O13" t="n">
         <v>183</v>
@@ -1717,7 +1717,7 @@
         <v>1900</v>
       </c>
       <c r="N15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O15" t="n">
         <v>159</v>
@@ -1803,7 +1803,7 @@
         <v>1900</v>
       </c>
       <c r="N16" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O16" t="n">
         <v>102</v>
@@ -1889,7 +1889,7 @@
         <v>1900</v>
       </c>
       <c r="N17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O17" t="n">
         <v>197</v>
@@ -1975,7 +1975,7 @@
         <v>1935</v>
       </c>
       <c r="N18" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O18" t="n">
         <v>201</v>
@@ -2061,7 +2061,7 @@
         <v>1989</v>
       </c>
       <c r="N19" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O19" t="n">
         <v>187</v>
@@ -2149,7 +2149,7 @@
         <v>1957</v>
       </c>
       <c r="N20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O20" t="n">
         <v>212</v>
@@ -2190,17 +2190,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Single Family Residential</t>
+          <t>Multi-Family (2-4 Unit)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1156 South St</t>
+          <t>534 Haws Ave</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Pottstown</t>
+          <t>Norristown</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2209,36 +2209,34 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>19464</v>
+        <v>19401</v>
       </c>
       <c r="G21" t="n">
         <v>389900</v>
       </c>
       <c r="H21" t="n">
-        <v>3</v>
-      </c>
-      <c r="I21" t="n">
-        <v>2.5</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Pottstown</t>
+          <t>Norristown</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>1906</v>
+        <v>2778</v>
       </c>
       <c r="L21" t="n">
-        <v>4200</v>
+        <v>3640</v>
       </c>
       <c r="M21" t="n">
-        <v>2005</v>
+        <v>1899</v>
       </c>
       <c r="N21" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="O21" t="n">
-        <v>205</v>
+        <v>140</v>
       </c>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr">
@@ -2248,7 +2246,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Pottstown/1156-South-St-19464/home/37966768</t>
+          <t>https://www.redfin.com/PA/Norristown/534-Haws-Ave-19401/home/38105368</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2258,7 +2256,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>PAMC2190414</t>
+          <t>PAMC2190620</t>
         </is>
       </c>
       <c r="U21" t="n">
@@ -2276,17 +2274,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Multi-Family (2-4 Unit)</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>534 Haws Ave</t>
+          <t>3000 Melina Ct</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Norristown</t>
+          <t>Bensalem</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2295,34 +2293,36 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>19401</v>
+        <v>19020</v>
       </c>
       <c r="G22" t="n">
         <v>389900</v>
       </c>
       <c r="H22" t="n">
-        <v>5</v>
-      </c>
-      <c r="I22" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2</v>
+      </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Norristown</t>
+          <t>NESHAMINY VALLEY</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>2778</v>
+        <v>1920</v>
       </c>
       <c r="L22" t="n">
-        <v>3640</v>
+        <v>3049</v>
       </c>
       <c r="M22" t="n">
-        <v>1899</v>
+        <v>1980</v>
       </c>
       <c r="N22" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="O22" t="n">
-        <v>140</v>
+        <v>203</v>
       </c>
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr">
@@ -2332,7 +2332,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Norristown/534-Haws-Ave-19401/home/38105368</t>
+          <t>https://www.redfin.com/PA/Bensalem/3000-Melina-Ct-19020/home/38397238</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>PAMC2190620</t>
+          <t>PABU2129244</t>
         </is>
       </c>
       <c r="U22" t="n">
@@ -2360,12 +2360,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>3000 Melina Ct</t>
+          <t>3379 Bristol Pike</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2382,13 +2382,13 @@
         <v>19020</v>
       </c>
       <c r="G23" t="n">
-        <v>389900</v>
+        <v>399900</v>
       </c>
       <c r="H23" t="n">
         <v>3</v>
       </c>
       <c r="I23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -2396,19 +2396,19 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>1920</v>
+        <v>1953</v>
       </c>
       <c r="L23" t="n">
-        <v>3049</v>
+        <v>8040</v>
       </c>
       <c r="M23" t="n">
-        <v>1980</v>
+        <v>1857</v>
       </c>
       <c r="N23" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="O23" t="n">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr">
@@ -2418,7 +2418,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Bensalem/3000-Melina-Ct-19020/home/38397238</t>
+          <t>https://www.redfin.com/PA/Bensalem/3379-Bristol-Pike-19020/home/38414380</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2428,11 +2428,11 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>PABU2129244</t>
+          <t>PABU2129808</t>
         </is>
       </c>
       <c r="U23" t="n">
-        <v>389900</v>
+        <v>399900</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2446,12 +2446,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Single Family Residential</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>3379 Bristol Pike</t>
+          <t>1396 Arundel Way</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2474,27 +2474,27 @@
         <v>3</v>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>NESHAMINY VALLEY</t>
+          <t>JUDSON MDWS</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>1953</v>
+        <v>1932</v>
       </c>
       <c r="L24" t="n">
-        <v>8040</v>
+        <v>2000</v>
       </c>
       <c r="M24" t="n">
-        <v>1857</v>
+        <v>1974</v>
       </c>
       <c r="N24" t="n">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="O24" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Bensalem/3379-Bristol-Pike-19020/home/38414380</t>
+          <t>https://www.redfin.com/PA/Bensalem/1396-Arundel-Way-19020/home/38425581</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>PABU2129808</t>
+          <t>PABU2127002</t>
         </is>
       </c>
       <c r="U24" t="n">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1396 Arundel Way</t>
+          <t>6308 Militia Ct</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2554,33 +2554,33 @@
         <v>19020</v>
       </c>
       <c r="G25" t="n">
-        <v>399900</v>
+        <v>410000</v>
       </c>
       <c r="H25" t="n">
         <v>3</v>
       </c>
       <c r="I25" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>JUDSON MDWS</t>
+          <t>NESHAMINY VALLEY</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>1932</v>
+        <v>2076</v>
       </c>
       <c r="L25" t="n">
-        <v>2000</v>
+        <v>3100</v>
       </c>
       <c r="M25" t="n">
-        <v>1974</v>
+        <v>1972</v>
       </c>
       <c r="N25" t="n">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="O25" t="n">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Bensalem/1396-Arundel-Way-19020/home/38425581</t>
+          <t>https://www.redfin.com/PA/Bensalem/6308-Militia-Ct-19020/home/38422245</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -2600,11 +2600,11 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>PABU2127002</t>
+          <t>PABU2128624</t>
         </is>
       </c>
       <c r="U25" t="n">
-        <v>399900</v>
+        <v>410000</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2623,12 +2623,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>6308 Militia Ct</t>
+          <t>641 Muhlenberg Dr</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Bensalem</t>
+          <t>Collegeville</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2637,38 +2637,38 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>19020</v>
+        <v>19426</v>
       </c>
       <c r="G26" t="n">
-        <v>410000</v>
+        <v>414900</v>
       </c>
       <c r="H26" t="n">
         <v>3</v>
       </c>
       <c r="I26" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>NESHAMINY VALLEY</t>
+          <t>Trappe</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>2076</v>
-      </c>
-      <c r="L26" t="n">
-        <v>3100</v>
-      </c>
+        <v>2078</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
       <c r="M26" t="n">
-        <v>1972</v>
+        <v>1997</v>
       </c>
       <c r="N26" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="O26" t="n">
-        <v>197</v>
-      </c>
-      <c r="P26" t="inlineStr"/>
+        <v>200</v>
+      </c>
+      <c r="P26" t="n">
+        <v>325</v>
+      </c>
       <c r="Q26" t="inlineStr">
         <is>
           <t>Active</t>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Bensalem/6308-Militia-Ct-19020/home/38422245</t>
+          <t>https://www.redfin.com/PA/Collegeville/641-Muhlenberg-Dr-19426/home/205182960</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -2686,11 +2686,11 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>PABU2128624</t>
+          <t>PAMC2192486</t>
         </is>
       </c>
       <c r="U26" t="n">
-        <v>410000</v>
+        <v>414900</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -2709,12 +2709,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>641 Muhlenberg Dr</t>
+          <t>1340 Markley St</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Collegeville</t>
+          <t>Norristown</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>19426</v>
+        <v>19401</v>
       </c>
       <c r="G27" t="n">
-        <v>414900</v>
+        <v>424900</v>
       </c>
       <c r="H27" t="n">
         <v>3</v>
@@ -2736,25 +2736,25 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Trappe</t>
+          <t>Norristown</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>2078</v>
-      </c>
-      <c r="L27" t="inlineStr"/>
+        <v>1939</v>
+      </c>
+      <c r="L27" t="n">
+        <v>3766</v>
+      </c>
       <c r="M27" t="n">
-        <v>1997</v>
+        <v>2026</v>
       </c>
       <c r="N27" t="n">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="O27" t="n">
-        <v>200</v>
-      </c>
-      <c r="P27" t="n">
-        <v>325</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr">
         <is>
           <t>Active</t>
@@ -2762,7 +2762,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Collegeville/641-Muhlenberg-Dr-19426/home/205182960</t>
+          <t>https://www.redfin.com/PA/Norristown/1340-Markley-St-19401/home/38109996</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -2772,11 +2772,11 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>PAMC2192486</t>
+          <t>PAMC2189340</t>
         </is>
       </c>
       <c r="U27" t="n">
-        <v>414900</v>
+        <v>424900</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1340 Markley St</t>
+          <t>1342 Markley St</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2829,13 +2829,13 @@
         <v>1939</v>
       </c>
       <c r="L28" t="n">
-        <v>3766</v>
+        <v>3931</v>
       </c>
       <c r="M28" t="n">
         <v>2026</v>
       </c>
       <c r="N28" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O28" t="n">
         <v>219</v>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Norristown/1340-Markley-St-19401/home/38109996</t>
+          <t>https://www.redfin.com/PA/Norristown/1342-Markley-St-19401/home/40524749</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>PAMC2189340</t>
+          <t>PAMC2189294</t>
         </is>
       </c>
       <c r="U28" t="n">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1342 Markley St</t>
+          <t>521 E Moore St</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2898,33 +2898,33 @@
         <v>19401</v>
       </c>
       <c r="G29" t="n">
-        <v>424900</v>
+        <v>433000</v>
       </c>
       <c r="H29" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I29" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Norristown</t>
+          <t>NORRISTOWN</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>1939</v>
+        <v>2972</v>
       </c>
       <c r="L29" t="n">
-        <v>3931</v>
+        <v>4080</v>
       </c>
       <c r="M29" t="n">
-        <v>2026</v>
+        <v>1900</v>
       </c>
       <c r="N29" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="O29" t="n">
-        <v>219</v>
+        <v>146</v>
       </c>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Norristown/1342-Markley-St-19401/home/40524749</t>
+          <t>https://www.redfin.com/PA/Norristown/521-E-Moore-St-19401/home/38111896</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -2944,11 +2944,11 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>PAMC2189294</t>
+          <t>PAMC2189894</t>
         </is>
       </c>
       <c r="U29" t="n">
-        <v>424900</v>
+        <v>433000</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -2962,12 +2962,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Single Family Residential</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>521 E Moore St</t>
+          <t>31 Bristol Ct</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2981,38 +2981,40 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>19401</v>
+        <v>19403</v>
       </c>
       <c r="G30" t="n">
-        <v>433000</v>
+        <v>437900</v>
       </c>
       <c r="H30" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I30" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>NORRISTOWN</t>
+          <t>BERWICK PL</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>2972</v>
+        <v>2064</v>
       </c>
       <c r="L30" t="n">
-        <v>4080</v>
+        <v>871</v>
       </c>
       <c r="M30" t="n">
-        <v>1900</v>
+        <v>1995</v>
       </c>
       <c r="N30" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="O30" t="n">
-        <v>146</v>
-      </c>
-      <c r="P30" t="inlineStr"/>
+        <v>212</v>
+      </c>
+      <c r="P30" t="n">
+        <v>250</v>
+      </c>
       <c r="Q30" t="inlineStr">
         <is>
           <t>Active</t>
@@ -3020,7 +3022,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Norristown/521-E-Moore-St-19401/home/38111896</t>
+          <t>https://www.redfin.com/PA/Norristown/31-Bristol-Ct-19403/home/39126069</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3030,11 +3032,11 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>PAMC2189894</t>
+          <t>PAMC2192914</t>
         </is>
       </c>
       <c r="U30" t="n">
-        <v>433000</v>
+        <v>437900</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
@@ -3053,12 +3055,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>31 Bristol Ct</t>
+          <t>1503 Seneca Run</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Norristown</t>
+          <t>Ambler</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3067,10 +3069,10 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>19403</v>
+        <v>19002</v>
       </c>
       <c r="G31" t="n">
-        <v>437900</v>
+        <v>449000</v>
       </c>
       <c r="H31" t="n">
         <v>3</v>
@@ -3080,35 +3082,35 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>BERWICK PL</t>
+          <t>ARROWHEAD</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>2064</v>
+        <v>1873</v>
       </c>
       <c r="L31" t="n">
-        <v>871</v>
+        <v>1600</v>
       </c>
       <c r="M31" t="n">
-        <v>1995</v>
+        <v>1984</v>
       </c>
       <c r="N31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O31" t="n">
-        <v>212</v>
+        <v>240</v>
       </c>
       <c r="P31" t="n">
-        <v>250</v>
+        <v>139</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>Pre On-Market</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Norristown/31-Bristol-Ct-19403/home/39126069</t>
+          <t>https://www.redfin.com/PA/Ambler/1503-Seneca-Run-19002/home/38912707</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3118,11 +3120,11 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>PAMC2192914</t>
+          <t>PAMC2191882</t>
         </is>
       </c>
       <c r="U31" t="n">
-        <v>437900</v>
+        <v>449000</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
@@ -3141,12 +3143,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1503 Seneca Run</t>
+          <t>2023 Ryans Run</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Ambler</t>
+          <t>Lansdale</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3155,7 +3157,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>19002</v>
+        <v>19446</v>
       </c>
       <c r="G32" t="n">
         <v>449000</v>
@@ -3168,26 +3170,26 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>ARROWHEAD</t>
+          <t>RYANS RUN</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>1873</v>
+        <v>2552</v>
       </c>
       <c r="L32" t="n">
-        <v>1600</v>
+        <v>1430</v>
       </c>
       <c r="M32" t="n">
-        <v>1984</v>
+        <v>1990</v>
       </c>
       <c r="N32" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="O32" t="n">
-        <v>240</v>
+        <v>176</v>
       </c>
       <c r="P32" t="n">
-        <v>139</v>
+        <v>250</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -3196,7 +3198,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Ambler/1503-Seneca-Run-19002/home/38912707</t>
+          <t>https://www.redfin.com/PA/Lansdale/2023-Ryans-Run-19446/home/38941395</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3206,7 +3208,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>PAMC2191882</t>
+          <t>PAMC2190996</t>
         </is>
       </c>
       <c r="U32" t="n">
@@ -3229,12 +3231,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2023 Ryans Run</t>
+          <t>381 Manor Cir</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Lansdale</t>
+          <t>Harleysville</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3243,39 +3245,39 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>19446</v>
+        <v>19438</v>
       </c>
       <c r="G33" t="n">
-        <v>449000</v>
+        <v>449900</v>
       </c>
       <c r="H33" t="n">
         <v>3</v>
       </c>
       <c r="I33" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>RYANS RUN</t>
+          <t>EDGEWOOD TERRACE</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>2552</v>
+        <v>1894</v>
       </c>
       <c r="L33" t="n">
-        <v>1430</v>
+        <v>4201</v>
       </c>
       <c r="M33" t="n">
-        <v>1990</v>
+        <v>2007</v>
       </c>
       <c r="N33" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="O33" t="n">
-        <v>176</v>
+        <v>238</v>
       </c>
       <c r="P33" t="n">
-        <v>250</v>
+        <v>140</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -3284,7 +3286,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Lansdale/2023-Ryans-Run-19446/home/38941395</t>
+          <t>https://www.redfin.com/PA/Harleysville/381-Manor-Cir-19438/home/37991223</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -3294,11 +3296,11 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>PAMC2190996</t>
+          <t>PAMC2189108</t>
         </is>
       </c>
       <c r="U33" t="n">
-        <v>449000</v>
+        <v>449900</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
@@ -3312,17 +3314,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>381 Manor Cir</t>
+          <t>3901 Beth Dr</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Harleysville</t>
+          <t>Collegeville</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3331,40 +3333,38 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>19438</v>
+        <v>19426</v>
       </c>
       <c r="G34" t="n">
-        <v>449900</v>
+        <v>450000</v>
       </c>
       <c r="H34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I34" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>EDGEWOOD TERRACE</t>
+          <t>Collegeville</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>1894</v>
+        <v>2166</v>
       </c>
       <c r="L34" t="n">
-        <v>4201</v>
+        <v>30000</v>
       </c>
       <c r="M34" t="n">
-        <v>2007</v>
+        <v>1965</v>
       </c>
       <c r="N34" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="O34" t="n">
-        <v>238</v>
-      </c>
-      <c r="P34" t="n">
-        <v>140</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr">
         <is>
           <t>Active</t>
@@ -3372,7 +3372,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Harleysville/381-Manor-Cir-19438/home/37991223</t>
+          <t>https://www.redfin.com/PA/Collegeville/3901-Beth-Dr-19426/home/38626788</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -3382,11 +3382,11 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>PAMC2189108</t>
+          <t>PAMC2192370</t>
         </is>
       </c>
       <c r="U34" t="n">
-        <v>449900</v>
+        <v>450000</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
@@ -3400,17 +3400,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>129 Cobblestone Dr Unit 4-25</t>
+          <t>282 Glendale Ave</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Harleysville</t>
+          <t>Pottstown</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3419,38 +3419,38 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>19438</v>
+        <v>19464</v>
       </c>
       <c r="G35" t="n">
-        <v>449900</v>
+        <v>459000</v>
       </c>
       <c r="H35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I35" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>THE FIELDS AT JACOBS WAY</t>
+          <t>Pottstown</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>1883</v>
+        <v>2568</v>
       </c>
       <c r="L35" t="n">
-        <v>1179</v>
-      </c>
-      <c r="M35" t="inlineStr"/>
+        <v>18730</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1947</v>
+      </c>
       <c r="N35" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="O35" t="n">
-        <v>239</v>
-      </c>
-      <c r="P35" t="n">
-        <v>177</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr">
         <is>
           <t>Active</t>
@@ -3458,7 +3458,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Harleysville/129-Cobblestone-Dr-19438/unit-4-25/home/202715281</t>
+          <t>https://www.redfin.com/PA/Pottstown/282-Glendale-Ave-19464/home/39027831</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -3468,11 +3468,11 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>PAMC2189570</t>
+          <t>PAMC2190402</t>
         </is>
       </c>
       <c r="U35" t="n">
-        <v>449900</v>
+        <v>459000</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -3491,12 +3491,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>3901 Beth Dr</t>
+          <t>809 Gabriel Ct</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Collegeville</t>
+          <t>Pottstown</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3505,46 +3505,46 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>19426</v>
+        <v>19464</v>
       </c>
       <c r="G36" t="n">
-        <v>450000</v>
+        <v>470000</v>
       </c>
       <c r="H36" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I36" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Collegeville</t>
+          <t>POTTSGROVE</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>2166</v>
+        <v>2201</v>
       </c>
       <c r="L36" t="n">
-        <v>30000</v>
+        <v>25737</v>
       </c>
       <c r="M36" t="n">
-        <v>1965</v>
+        <v>1979</v>
       </c>
       <c r="N36" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O36" t="n">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Pre On-Market</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Collegeville/3901-Beth-Dr-19426/home/38626788</t>
+          <t>https://www.redfin.com/PA/Pottstown/809-Gabriel-Ct-19464/home/38605524</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -3554,11 +3554,11 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>PAMC2192370</t>
+          <t>PAMC2192448</t>
         </is>
       </c>
       <c r="U36" t="n">
-        <v>450000</v>
+        <v>470000</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -3572,17 +3572,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Single Family Residential</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>282 Glendale Ave</t>
+          <t>106 Henning Dr</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Pottstown</t>
+          <t>North Wales</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3591,36 +3591,36 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>19464</v>
+        <v>19454</v>
       </c>
       <c r="G37" t="n">
-        <v>459000</v>
+        <v>475000</v>
       </c>
       <c r="H37" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I37" t="n">
         <v>2.5</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Pottstown</t>
+          <t>THE ORCHARD</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>2568</v>
+        <v>1841</v>
       </c>
       <c r="L37" t="n">
-        <v>18730</v>
+        <v>3029</v>
       </c>
       <c r="M37" t="n">
-        <v>1947</v>
+        <v>1988</v>
       </c>
       <c r="N37" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="O37" t="n">
-        <v>179</v>
+        <v>258</v>
       </c>
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Pottstown/282-Glendale-Ave-19464/home/39027831</t>
+          <t>https://www.redfin.com/PA/North-Wales/106-Henning-Dr-19454/home/38690465</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -3640,11 +3640,11 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>PAMC2190402</t>
+          <t>PAMC2191858</t>
         </is>
       </c>
       <c r="U37" t="n">
-        <v>459000</v>
+        <v>475000</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -3658,17 +3658,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Single Family Residential</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>809 Gabriel Ct</t>
+          <t>119 Farrington Ct</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Pottstown</t>
+          <t>Collegeville</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3677,10 +3677,10 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>19464</v>
+        <v>19426</v>
       </c>
       <c r="G38" t="n">
-        <v>470000</v>
+        <v>475000</v>
       </c>
       <c r="H38" t="n">
         <v>3</v>
@@ -3690,33 +3690,35 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>POTTSGROVE</t>
+          <t>PROVIDENCE VIEW</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>2201</v>
+        <v>2284</v>
       </c>
       <c r="L38" t="n">
-        <v>25737</v>
+        <v>1684</v>
       </c>
       <c r="M38" t="n">
-        <v>1979</v>
+        <v>1997</v>
       </c>
       <c r="N38" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="O38" t="n">
-        <v>214</v>
-      </c>
-      <c r="P38" t="inlineStr"/>
+        <v>208</v>
+      </c>
+      <c r="P38" t="n">
+        <v>375</v>
+      </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>Pre On-Market</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Pottstown/809-Gabriel-Ct-19464/home/38605524</t>
+          <t>https://www.redfin.com/PA/Collegeville/119-Farrington-Ct-19426/home/39042101</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -3726,11 +3728,11 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>PAMC2192448</t>
+          <t>PAMC2191362</t>
         </is>
       </c>
       <c r="U38" t="n">
-        <v>470000</v>
+        <v>475000</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -3749,12 +3751,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>106 Henning Dr</t>
+          <t>101 Walker Rd</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>North Wales</t>
+          <t>Royersford</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3763,7 +3765,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>19454</v>
+        <v>19468</v>
       </c>
       <c r="G39" t="n">
         <v>475000</v>
@@ -3776,25 +3778,27 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>THE ORCHARD</t>
+          <t>THE LINKS AT SPRIN</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>1841</v>
+        <v>1849</v>
       </c>
       <c r="L39" t="n">
-        <v>3029</v>
+        <v>3066</v>
       </c>
       <c r="M39" t="n">
-        <v>1988</v>
+        <v>1999</v>
       </c>
       <c r="N39" t="n">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="O39" t="n">
-        <v>258</v>
-      </c>
-      <c r="P39" t="inlineStr"/>
+        <v>257</v>
+      </c>
+      <c r="P39" t="n">
+        <v>207</v>
+      </c>
       <c r="Q39" t="inlineStr">
         <is>
           <t>Active</t>
@@ -3802,7 +3806,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/North-Wales/106-Henning-Dr-19454/home/38690465</t>
+          <t>https://www.redfin.com/PA/Royersford/101-Walker-Rd-19468/home/39132339</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -3812,7 +3816,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>PAMC2191858</t>
+          <t>PAMC2187842</t>
         </is>
       </c>
       <c r="U39" t="n">
@@ -3835,12 +3839,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>119 Farrington Ct</t>
+          <t>703 Green St</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Collegeville</t>
+          <t>Bridgeport</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3849,40 +3853,38 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>19426</v>
+        <v>19405</v>
       </c>
       <c r="G40" t="n">
         <v>475000</v>
       </c>
       <c r="H40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I40" t="n">
         <v>2.5</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>PROVIDENCE VIEW</t>
+          <t>Bridgeport</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>2284</v>
+        <v>2324</v>
       </c>
       <c r="L40" t="n">
-        <v>1684</v>
+        <v>2426</v>
       </c>
       <c r="M40" t="n">
-        <v>1997</v>
+        <v>2005</v>
       </c>
       <c r="N40" t="n">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="O40" t="n">
-        <v>208</v>
-      </c>
-      <c r="P40" t="n">
-        <v>375</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr">
         <is>
           <t>Active</t>
@@ -3890,7 +3892,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Collegeville/119-Farrington-Ct-19426/home/39042101</t>
+          <t>https://www.redfin.com/PA/Bridgeport/703-Green-St-19405/home/37971740</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -3900,7 +3902,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>PAMC2191362</t>
+          <t>PAMC2187186</t>
         </is>
       </c>
       <c r="U40" t="n">
@@ -3918,12 +3920,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>101 Walker Rd</t>
+          <t>136 Souder Rd</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3943,34 +3945,32 @@
         <v>475000</v>
       </c>
       <c r="H41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I41" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>THE LINKS AT SPRIN</t>
+          <t>Royersford</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>1849</v>
+        <v>2181</v>
       </c>
       <c r="L41" t="n">
-        <v>3066</v>
+        <v>62400</v>
       </c>
       <c r="M41" t="n">
-        <v>1999</v>
+        <v>1830</v>
       </c>
       <c r="N41" t="n">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="O41" t="n">
-        <v>257</v>
-      </c>
-      <c r="P41" t="n">
-        <v>207</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr">
         <is>
           <t>Active</t>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Royersford/101-Walker-Rd-19468/home/39132339</t>
+          <t>https://www.redfin.com/PA/Royersford/136-Souder-Rd-19468/home/38440543</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>PAMC2187842</t>
+          <t>PAMC2171178</t>
         </is>
       </c>
       <c r="U41" t="n">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>703 Green St</t>
+          <t>5 Abbott Ct</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Bridgeport</t>
+          <t>Eagleville</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4025,38 +4025,40 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>19405</v>
+        <v>19403</v>
       </c>
       <c r="G42" t="n">
-        <v>475000</v>
+        <v>479000</v>
       </c>
       <c r="H42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I42" t="n">
         <v>2.5</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Bridgeport</t>
+          <t>CHADWICK PL</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>2324</v>
+        <v>2460</v>
       </c>
       <c r="L42" t="n">
-        <v>2426</v>
+        <v>1152</v>
       </c>
       <c r="M42" t="n">
-        <v>2005</v>
+        <v>1997</v>
       </c>
       <c r="N42" t="n">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="O42" t="n">
-        <v>204</v>
-      </c>
-      <c r="P42" t="inlineStr"/>
+        <v>195</v>
+      </c>
+      <c r="P42" t="n">
+        <v>135</v>
+      </c>
       <c r="Q42" t="inlineStr">
         <is>
           <t>Active</t>
@@ -4064,7 +4066,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Bridgeport/703-Green-St-19405/home/37971740</t>
+          <t>https://www.redfin.com/PA/Eagleville/5-Abbott-Ct-19403/home/39126185</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -4074,11 +4076,11 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>PAMC2187186</t>
+          <t>PAMC2192124</t>
         </is>
       </c>
       <c r="U42" t="n">
-        <v>475000</v>
+        <v>479000</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -4092,17 +4094,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Single Family Residential</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>136 Souder Rd</t>
+          <t>1879 Arbor Place Dr Lot 65</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Royersford</t>
+          <t>Norristown</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4111,38 +4113,38 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>19468</v>
+        <v>19401</v>
       </c>
       <c r="G43" t="n">
-        <v>475000</v>
+        <v>479900</v>
       </c>
       <c r="H43" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I43" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Royersford</t>
+          <t>ARBOR PLACE</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>2181</v>
-      </c>
-      <c r="L43" t="n">
-        <v>62400</v>
-      </c>
+        <v>1923</v>
+      </c>
+      <c r="L43" t="inlineStr"/>
       <c r="M43" t="n">
-        <v>1830</v>
+        <v>2026</v>
       </c>
       <c r="N43" t="n">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="O43" t="n">
-        <v>218</v>
-      </c>
-      <c r="P43" t="inlineStr"/>
+        <v>250</v>
+      </c>
+      <c r="P43" t="n">
+        <v>195</v>
+      </c>
       <c r="Q43" t="inlineStr">
         <is>
           <t>Active</t>
@@ -4150,7 +4152,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Royersford/136-Souder-Rd-19468/home/38440543</t>
+          <t>https://www.redfin.com/PA/Norristown/1879-Arbor-Place-Dr-19401/unit-65/home/203251592</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -4160,11 +4162,11 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>PAMC2171178</t>
+          <t>PAMC2192226</t>
         </is>
       </c>
       <c r="U43" t="n">
-        <v>475000</v>
+        <v>479900</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -4178,17 +4180,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>5 Abbott Ct</t>
+          <t>104 Farview Ave</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Eagleville</t>
+          <t>Norristown</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4200,37 +4202,35 @@
         <v>19403</v>
       </c>
       <c r="G44" t="n">
-        <v>479000</v>
+        <v>480000</v>
       </c>
       <c r="H44" t="n">
         <v>3</v>
       </c>
       <c r="I44" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>CHADWICK PL</t>
+          <t>Norristown</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>2460</v>
+        <v>1966</v>
       </c>
       <c r="L44" t="n">
-        <v>1152</v>
+        <v>9568</v>
       </c>
       <c r="M44" t="n">
-        <v>1997</v>
+        <v>1952</v>
       </c>
       <c r="N44" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="O44" t="n">
-        <v>195</v>
-      </c>
-      <c r="P44" t="n">
-        <v>135</v>
-      </c>
+        <v>244</v>
+      </c>
+      <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr">
         <is>
           <t>Pre On-Market</t>
@@ -4238,7 +4238,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Eagleville/5-Abbott-Ct-19403/home/39126185</t>
+          <t>https://www.redfin.com/PA/Norristown/104-Farview-Ave-19403/home/38633637</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -4248,11 +4248,11 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>PAMC2192124</t>
+          <t>PAMC2189674</t>
         </is>
       </c>
       <c r="U44" t="n">
-        <v>479000</v>
+        <v>480000</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -4266,17 +4266,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>1879 Arbor Place Dr Lot 65</t>
+          <t>733 S Park Ave</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Norristown</t>
+          <t>Audubon</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4285,38 +4285,38 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>19401</v>
+        <v>19403</v>
       </c>
       <c r="G45" t="n">
-        <v>479900</v>
+        <v>489000</v>
       </c>
       <c r="H45" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I45" t="n">
         <v>2.5</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>ARBOR PLACE</t>
+          <t>Audubon</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>1923</v>
-      </c>
-      <c r="L45" t="inlineStr"/>
+        <v>2286</v>
+      </c>
+      <c r="L45" t="n">
+        <v>19044</v>
+      </c>
       <c r="M45" t="n">
-        <v>2026</v>
+        <v>1969</v>
       </c>
       <c r="N45" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="O45" t="n">
-        <v>250</v>
-      </c>
-      <c r="P45" t="n">
-        <v>195</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr">
         <is>
           <t>Active</t>
@@ -4324,7 +4324,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Norristown/1879-Arbor-Place-Dr-19401/unit-65/home/203251592</t>
+          <t>https://www.redfin.com/PA/Audubon/733-S-Park-Ave-19403/home/38644026</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -4334,11 +4334,11 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>PAMC2192226</t>
+          <t>PAMC2189096</t>
         </is>
       </c>
       <c r="U45" t="n">
-        <v>479900</v>
+        <v>489000</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -4352,17 +4352,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Single Family Residential</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>104 Farview Ave</t>
+          <t>100 Susan Cir</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Norristown</t>
+          <t>North Wales</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4371,46 +4371,48 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>19403</v>
+        <v>19454</v>
       </c>
       <c r="G46" t="n">
-        <v>480000</v>
+        <v>490000</v>
       </c>
       <c r="H46" t="n">
         <v>3</v>
       </c>
       <c r="I46" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Norristown</t>
+          <t>GEN HANCOCK TOWNH A/K/A HIGHVIEW</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>1966</v>
+        <v>1972</v>
       </c>
       <c r="L46" t="n">
-        <v>9568</v>
+        <v>760</v>
       </c>
       <c r="M46" t="n">
-        <v>1952</v>
+        <v>2011</v>
       </c>
       <c r="N46" t="n">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="O46" t="n">
-        <v>244</v>
-      </c>
-      <c r="P46" t="inlineStr"/>
+        <v>248</v>
+      </c>
+      <c r="P46" t="n">
+        <v>218</v>
+      </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>Pre On-Market</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Norristown/104-Farview-Ave-19403/home/38633637</t>
+          <t>https://www.redfin.com/PA/North-Wales/100-Susan-Cir-19454/home/40524679</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -4420,11 +4422,11 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>PAMC2189674</t>
+          <t>PAMC2191382</t>
         </is>
       </c>
       <c r="U46" t="n">
-        <v>480000</v>
+        <v>490000</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
@@ -4438,17 +4440,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Single Family Residential</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>733 S Park Ave</t>
+          <t>1047 Chapman Cir</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Audubon</t>
+          <t>Hatfield</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4457,38 +4459,38 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>19403</v>
+        <v>19440</v>
       </c>
       <c r="G47" t="n">
-        <v>489000</v>
+        <v>494900</v>
       </c>
       <c r="H47" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I47" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Audubon</t>
+          <t>FORTUNASTATION</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>2286</v>
-      </c>
-      <c r="L47" t="n">
-        <v>19044</v>
-      </c>
+        <v>2360</v>
+      </c>
+      <c r="L47" t="inlineStr"/>
       <c r="M47" t="n">
-        <v>1969</v>
+        <v>2019</v>
       </c>
       <c r="N47" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="O47" t="n">
-        <v>214</v>
-      </c>
-      <c r="P47" t="inlineStr"/>
+        <v>210</v>
+      </c>
+      <c r="P47" t="n">
+        <v>210</v>
+      </c>
       <c r="Q47" t="inlineStr">
         <is>
           <t>Active</t>
@@ -4496,7 +4498,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Audubon/733-S-Park-Ave-19403/home/38644026</t>
+          <t>https://www.redfin.com/PA/Hatfield/1047-Chapman-Cir-19440/home/170666841</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -4506,11 +4508,11 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>PAMC2189096</t>
+          <t>PAMC2189254</t>
         </is>
       </c>
       <c r="U47" t="n">
-        <v>489000</v>
+        <v>494900</v>
       </c>
       <c r="V47" t="n">
         <v>0</v>
@@ -4529,12 +4531,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>100 Susan Cir</t>
+          <t>196 Hudson Dr</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>North Wales</t>
+          <t>Phoenixville</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -4543,48 +4545,48 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>19454</v>
+        <v>19460</v>
       </c>
       <c r="G48" t="n">
-        <v>490000</v>
+        <v>495000</v>
       </c>
       <c r="H48" t="n">
         <v>3</v>
       </c>
       <c r="I48" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>GEN HANCOCK TOWNH A/K/A HIGHVIEW</t>
+          <t>LONGFORD CROSSING</t>
         </is>
       </c>
       <c r="K48" t="n">
-        <v>1972</v>
+        <v>1900</v>
       </c>
       <c r="L48" t="n">
-        <v>760</v>
+        <v>963</v>
       </c>
       <c r="M48" t="n">
-        <v>2011</v>
+        <v>2007</v>
       </c>
       <c r="N48" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="O48" t="n">
-        <v>248</v>
+        <v>261</v>
       </c>
       <c r="P48" t="n">
-        <v>218</v>
+        <v>120</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Pre On-Market</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/North-Wales/100-Susan-Cir-19454/home/40524679</t>
+          <t>https://www.redfin.com/PA/Phoenixville/196-Hudson-Dr-19460/home/37980863</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -4594,11 +4596,11 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>PAMC2191382</t>
+          <t>PAMC2191244</t>
         </is>
       </c>
       <c r="U48" t="n">
-        <v>490000</v>
+        <v>495000</v>
       </c>
       <c r="V48" t="n">
         <v>0</v>
@@ -4617,12 +4619,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>1047 Chapman Cir</t>
+          <t>32 Charter Oak Ct</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Hatfield</t>
+          <t>Doylestown</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -4631,37 +4633,37 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>19440</v>
+        <v>18901</v>
       </c>
       <c r="G49" t="n">
-        <v>494900</v>
+        <v>498500</v>
       </c>
       <c r="H49" t="n">
         <v>3</v>
       </c>
       <c r="I49" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>FORTUNASTATION</t>
+          <t>DOYLESTOWN STATION</t>
         </is>
       </c>
       <c r="K49" t="n">
-        <v>2360</v>
+        <v>2024</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="n">
-        <v>2019</v>
+        <v>1998</v>
       </c>
       <c r="N49" t="n">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="O49" t="n">
-        <v>210</v>
+        <v>246</v>
       </c>
       <c r="P49" t="n">
-        <v>210</v>
+        <v>309</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -4670,7 +4672,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Hatfield/1047-Chapman-Cir-19440/home/170666841</t>
+          <t>https://www.redfin.com/PA/Doylestown/32-Charter-Oak-Ct-18901/home/38606215</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -4680,11 +4682,11 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>PAMC2189254</t>
+          <t>PABU2126142</t>
         </is>
       </c>
       <c r="U49" t="n">
-        <v>494900</v>
+        <v>498500</v>
       </c>
       <c r="V49" t="n">
         <v>0</v>
@@ -4698,17 +4700,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>196 Hudson Dr</t>
+          <t>90 E Ninth</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Phoenixville</t>
+          <t>Collegeville</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -4717,40 +4719,38 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>19460</v>
+        <v>19426</v>
       </c>
       <c r="G50" t="n">
-        <v>495000</v>
+        <v>499000</v>
       </c>
       <c r="H50" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I50" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>LONGFORD CROSSING</t>
+          <t>Collegeville</t>
         </is>
       </c>
       <c r="K50" t="n">
-        <v>1900</v>
+        <v>3173</v>
       </c>
       <c r="L50" t="n">
-        <v>963</v>
+        <v>36324</v>
       </c>
       <c r="M50" t="n">
-        <v>2007</v>
+        <v>1949</v>
       </c>
       <c r="N50" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="O50" t="n">
-        <v>261</v>
-      </c>
-      <c r="P50" t="n">
-        <v>120</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr">
         <is>
           <t>Pre On-Market</t>
@@ -4758,7 +4758,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Phoenixville/196-Hudson-Dr-19460/home/37980863</t>
+          <t>https://www.redfin.com/PA/Collegeville/90-E-9th-Ave-19426/home/38041907</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -4768,11 +4768,11 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>PAMC2191244</t>
+          <t>PAMC2187712</t>
         </is>
       </c>
       <c r="U50" t="n">
-        <v>495000</v>
+        <v>499000</v>
       </c>
       <c r="V50" t="n">
         <v>0</v>
@@ -4786,17 +4786,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>32 Charter Oak Ct</t>
+          <t>2907 Kanes Rd</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Doylestown</t>
+          <t>Willow Grove</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -4805,38 +4805,38 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>18901</v>
+        <v>19090</v>
       </c>
       <c r="G51" t="n">
-        <v>498500</v>
+        <v>499000</v>
       </c>
       <c r="H51" t="n">
         <v>3</v>
       </c>
       <c r="I51" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>DOYLESTOWN STATION</t>
+          <t>WILLOW MANOR</t>
         </is>
       </c>
       <c r="K51" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L51" t="inlineStr"/>
+        <v>1974</v>
+      </c>
+      <c r="L51" t="n">
+        <v>7600</v>
+      </c>
       <c r="M51" t="n">
-        <v>1998</v>
+        <v>1956</v>
       </c>
       <c r="N51" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="O51" t="n">
-        <v>246</v>
-      </c>
-      <c r="P51" t="n">
-        <v>309</v>
-      </c>
+        <v>253</v>
+      </c>
+      <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr">
         <is>
           <t>Active</t>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Doylestown/32-Charter-Oak-Ct-18901/home/38606215</t>
+          <t>https://www.redfin.com/PA/Willow-Grove/2907-Kanes-Rd-19090/home/38224248</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -4854,11 +4854,11 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>PABU2126142</t>
+          <t>PAMC2189536</t>
         </is>
       </c>
       <c r="U51" t="n">
-        <v>498500</v>
+        <v>499000</v>
       </c>
       <c r="V51" t="n">
         <v>0</v>
@@ -4877,12 +4877,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>90 E Ninth</t>
+          <t>3118 Shirlene Rd</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Collegeville</t>
+          <t>East Norriton</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -4891,10 +4891,10 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>19426</v>
+        <v>19403</v>
       </c>
       <c r="G52" t="n">
-        <v>499000</v>
+        <v>499900</v>
       </c>
       <c r="H52" t="n">
         <v>4</v>
@@ -4904,33 +4904,33 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Collegeville</t>
+          <t>NORRISTOWN</t>
         </is>
       </c>
       <c r="K52" t="n">
-        <v>3173</v>
+        <v>2145</v>
       </c>
       <c r="L52" t="n">
-        <v>36324</v>
+        <v>13100</v>
       </c>
       <c r="M52" t="n">
-        <v>1949</v>
+        <v>1955</v>
       </c>
       <c r="N52" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O52" t="n">
-        <v>157</v>
+        <v>233</v>
       </c>
       <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>Pre On-Market</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Collegeville/90-E-9th-Ave-19426/home/38041907</t>
+          <t>https://www.redfin.com/PA/East-Norriton/3118-Shirlene-Rd-19403/home/38332887</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -4940,11 +4940,11 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>PAMC2187712</t>
+          <t>PAMC2191556</t>
         </is>
       </c>
       <c r="U52" t="n">
-        <v>499000</v>
+        <v>499900</v>
       </c>
       <c r="V52" t="n">
         <v>0</v>
@@ -4958,17 +4958,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Single Family Residential</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2907 Kanes Rd</t>
+          <t>306 Winding Way</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Willow Grove</t>
+          <t>King Of Prussia</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -4977,38 +4977,40 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>19090</v>
+        <v>19406</v>
       </c>
       <c r="G53" t="n">
-        <v>499000</v>
+        <v>499900</v>
       </c>
       <c r="H53" t="n">
         <v>3</v>
       </c>
       <c r="I53" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>WILLOW MANOR</t>
+          <t>CROOKED CROSSING</t>
         </is>
       </c>
       <c r="K53" t="n">
-        <v>1974</v>
+        <v>2129</v>
       </c>
       <c r="L53" t="n">
-        <v>7600</v>
+        <v>1865</v>
       </c>
       <c r="M53" t="n">
-        <v>1956</v>
+        <v>1987</v>
       </c>
       <c r="N53" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="O53" t="n">
-        <v>253</v>
-      </c>
-      <c r="P53" t="inlineStr"/>
+        <v>235</v>
+      </c>
+      <c r="P53" t="n">
+        <v>300</v>
+      </c>
       <c r="Q53" t="inlineStr">
         <is>
           <t>Active</t>
@@ -5016,7 +5018,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Willow-Grove/2907-Kanes-Rd-19090/home/38224248</t>
+          <t>https://www.redfin.com/PA/King-of-Prussia/306-Winding-Way-19406/home/39137235</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -5026,11 +5028,11 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>PAMC2189536</t>
+          <t>PAMC2192046</t>
         </is>
       </c>
       <c r="U53" t="n">
-        <v>499000</v>
+        <v>499900</v>
       </c>
       <c r="V53" t="n">
         <v>0</v>
@@ -5044,17 +5046,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Single Family Residential</t>
+          <t>Multi-Family (2-4 Unit)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>3118 Shirlene Rd</t>
+          <t>404 N Charlotte St</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>East Norriton</t>
+          <t>Pottstown</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5063,36 +5065,36 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>19403</v>
+        <v>19464</v>
       </c>
       <c r="G54" t="n">
-        <v>499900</v>
+        <v>500000</v>
       </c>
       <c r="H54" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I54" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>NORRISTOWN</t>
+          <t>POTTSTOWN</t>
         </is>
       </c>
       <c r="K54" t="n">
-        <v>2145</v>
+        <v>4878</v>
       </c>
       <c r="L54" t="n">
-        <v>13100</v>
+        <v>3049</v>
       </c>
       <c r="M54" t="n">
-        <v>1955</v>
+        <v>1910</v>
       </c>
       <c r="N54" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="O54" t="n">
-        <v>233</v>
+        <v>103</v>
       </c>
       <c r="P54" t="inlineStr"/>
       <c r="Q54" t="inlineStr">
@@ -5102,7 +5104,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/East-Norriton/3118-Shirlene-Rd-19403/home/38332887</t>
+          <t>https://www.redfin.com/PA/Pottstown/404-N-Charlotte-St-19464/home/86035387</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
@@ -5112,11 +5114,11 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>PAMC2191556</t>
+          <t>PAMC2191878</t>
         </is>
       </c>
       <c r="U54" t="n">
-        <v>499900</v>
+        <v>500000</v>
       </c>
       <c r="V54" t="n">
         <v>0</v>
@@ -5130,17 +5132,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Multi-Family (2-4 Unit)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>306 Winding Way</t>
+          <t>343 Summer Ave</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>King Of Prussia</t>
+          <t>Horsham</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5149,40 +5151,36 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>19406</v>
+        <v>19044</v>
       </c>
       <c r="G55" t="n">
-        <v>499900</v>
+        <v>500000</v>
       </c>
       <c r="H55" t="n">
-        <v>3</v>
-      </c>
-      <c r="I55" t="n">
-        <v>2.5</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
-          <t>CROOKED CROSSING</t>
+          <t>Horsham</t>
         </is>
       </c>
       <c r="K55" t="n">
-        <v>2129</v>
+        <v>2016</v>
       </c>
       <c r="L55" t="n">
-        <v>1865</v>
+        <v>28861</v>
       </c>
       <c r="M55" t="n">
-        <v>1987</v>
+        <v>1968</v>
       </c>
       <c r="N55" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="O55" t="n">
-        <v>235</v>
-      </c>
-      <c r="P55" t="n">
-        <v>300</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="P55" t="inlineStr"/>
       <c r="Q55" t="inlineStr">
         <is>
           <t>Active</t>
@@ -5190,7 +5188,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/King-of-Prussia/306-Winding-Way-19406/home/39137235</t>
+          <t>https://www.redfin.com/PA/Horsham/343-Summer-Ave-19044/home/38411682</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -5200,11 +5198,11 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>PAMC2192046</t>
+          <t>PAMC2188432</t>
         </is>
       </c>
       <c r="U55" t="n">
-        <v>499900</v>
+        <v>500000</v>
       </c>
       <c r="V55" t="n">
         <v>0</v>
@@ -5218,17 +5216,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Multi-Family (2-4 Unit)</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>404 N Charlotte St</t>
+          <t>710 Stafford Ct</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Pottstown</t>
+          <t>Chalfont</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5237,46 +5235,48 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>19464</v>
+        <v>18914</v>
       </c>
       <c r="G56" t="n">
         <v>500000</v>
       </c>
       <c r="H56" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I56" t="n">
         <v>2.5</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>POTTSTOWN</t>
+          <t>LONGMEADOW</t>
         </is>
       </c>
       <c r="K56" t="n">
-        <v>4878</v>
+        <v>2584</v>
       </c>
       <c r="L56" t="n">
-        <v>3049</v>
+        <v>3200</v>
       </c>
       <c r="M56" t="n">
-        <v>1910</v>
+        <v>1996</v>
       </c>
       <c r="N56" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="O56" t="n">
-        <v>103</v>
-      </c>
-      <c r="P56" t="inlineStr"/>
+        <v>193</v>
+      </c>
+      <c r="P56" t="n">
+        <v>175</v>
+      </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Pre On-Market</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Pottstown/404-N-Charlotte-St-19464/home/86035387</t>
+          <t>https://www.redfin.com/PA/Chalfont/710-Stafford-Ct-18914/home/38930255</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>PAMC2191878</t>
+          <t>PABU2128964</t>
         </is>
       </c>
       <c r="U56" t="n">
@@ -5304,17 +5304,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Multi-Family (2-4 Unit)</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>343 Summer Ave</t>
+          <t>2928 Windsor Dr</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Horsham</t>
+          <t>Bensalem</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5323,7 +5323,7 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>19044</v>
+        <v>19020</v>
       </c>
       <c r="G57" t="n">
         <v>500000</v>
@@ -5331,26 +5331,28 @@
       <c r="H57" t="n">
         <v>4</v>
       </c>
-      <c r="I57" t="inlineStr"/>
+      <c r="I57" t="n">
+        <v>2</v>
+      </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Horsham</t>
+          <t>NOTTINGHAM VIL</t>
         </is>
       </c>
       <c r="K57" t="n">
-        <v>2016</v>
+        <v>1950</v>
       </c>
       <c r="L57" t="n">
-        <v>28861</v>
+        <v>6000</v>
       </c>
       <c r="M57" t="n">
-        <v>1968</v>
+        <v>1955</v>
       </c>
       <c r="N57" t="n">
-        <v>39</v>
+        <v>105</v>
       </c>
       <c r="O57" t="n">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr">
@@ -5360,7 +5362,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Horsham/343-Summer-Ave-19044/home/38411682</t>
+          <t>https://www.redfin.com/PA/Bensalem/2928-Windsor-Dr-19020/home/38373879</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -5370,7 +5372,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>PAMC2188432</t>
+          <t>PABU2120968</t>
         </is>
       </c>
       <c r="U57" t="n">
@@ -5393,7 +5395,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>710 Stafford Ct</t>
+          <t>350 Glennbrook Way</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -5410,7 +5412,7 @@
         <v>18914</v>
       </c>
       <c r="G58" t="n">
-        <v>500000</v>
+        <v>510000</v>
       </c>
       <c r="H58" t="n">
         <v>3</v>
@@ -5420,35 +5422,33 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>LONGMEADOW</t>
+          <t>CHALFONT</t>
         </is>
       </c>
       <c r="K58" t="n">
-        <v>2584</v>
-      </c>
-      <c r="L58" t="n">
-        <v>3200</v>
-      </c>
+        <v>2157</v>
+      </c>
+      <c r="L58" t="inlineStr"/>
       <c r="M58" t="n">
-        <v>1996</v>
+        <v>1993</v>
       </c>
       <c r="N58" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="O58" t="n">
-        <v>193</v>
+        <v>236</v>
       </c>
       <c r="P58" t="n">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>Pre On-Market</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Chalfont/710-Stafford-Ct-18914/home/38930255</t>
+          <t>https://www.redfin.com/PA/Chalfont/350-Glennbrook-Way-18914/home/38922820</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -5458,11 +5458,11 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>PABU2128964</t>
+          <t>PABU2129794</t>
         </is>
       </c>
       <c r="U58" t="n">
-        <v>500000</v>
+        <v>510000</v>
       </c>
       <c r="V58" t="n">
         <v>0</v>
@@ -5481,12 +5481,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2928 Windsor Dr</t>
+          <t>152/154 N Main St</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Bensalem</t>
+          <t>Chalfont</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -5495,36 +5495,36 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>19020</v>
+        <v>18914</v>
       </c>
       <c r="G59" t="n">
-        <v>500000</v>
+        <v>510000</v>
       </c>
       <c r="H59" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I59" t="n">
         <v>2</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>NOTTINGHAM VIL</t>
+          <t>ROSEMORE ESTS</t>
         </is>
       </c>
       <c r="K59" t="n">
-        <v>1950</v>
+        <v>2093</v>
       </c>
       <c r="L59" t="n">
-        <v>6000</v>
+        <v>10450</v>
       </c>
       <c r="M59" t="n">
-        <v>1955</v>
+        <v>1920</v>
       </c>
       <c r="N59" t="n">
-        <v>104</v>
+        <v>167</v>
       </c>
       <c r="O59" t="n">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr">
@@ -5534,7 +5534,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Bensalem/2928-Windsor-Dr-19020/home/38373879</t>
+          <t>https://www.redfin.com/PA/Chalfont/152-N-Main-St-18914/home/38564500</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -5544,11 +5544,11 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>PABU2120968</t>
+          <t>PABU2116242</t>
         </is>
       </c>
       <c r="U59" t="n">
-        <v>500000</v>
+        <v>510000</v>
       </c>
       <c r="V59" t="n">
         <v>0</v>
@@ -5567,12 +5567,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>350 Glennbrook Way</t>
+          <t>625 E Walnut St</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Chalfont</t>
+          <t>North Wales</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -5581,38 +5581,38 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>18914</v>
+        <v>19454</v>
       </c>
       <c r="G60" t="n">
-        <v>510000</v>
+        <v>514900</v>
       </c>
       <c r="H60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I60" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>CHALFONT</t>
+          <t>North Wales</t>
         </is>
       </c>
       <c r="K60" t="n">
-        <v>2157</v>
-      </c>
-      <c r="L60" t="inlineStr"/>
+        <v>2520</v>
+      </c>
+      <c r="L60" t="n">
+        <v>6600</v>
+      </c>
       <c r="M60" t="n">
-        <v>1993</v>
+        <v>1908</v>
       </c>
       <c r="N60" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="O60" t="n">
-        <v>236</v>
-      </c>
-      <c r="P60" t="n">
-        <v>180</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr">
         <is>
           <t>Active</t>
@@ -5620,7 +5620,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Chalfont/350-Glennbrook-Way-18914/home/38922820</t>
+          <t>https://www.redfin.com/PA/North-Wales/625-E-Walnut-St-19454/home/38126535</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -5630,11 +5630,11 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>PABU2129794</t>
+          <t>PAMC2191428</t>
         </is>
       </c>
       <c r="U60" t="n">
-        <v>510000</v>
+        <v>514900</v>
       </c>
       <c r="V60" t="n">
         <v>0</v>
@@ -5648,17 +5648,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Single Family Residential</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>152/154 N Main St</t>
+          <t>306 East Sawyer Ct</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Chalfont</t>
+          <t>Royersford</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -5667,38 +5667,38 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>18914</v>
+        <v>19468</v>
       </c>
       <c r="G61" t="n">
-        <v>510000</v>
+        <v>514987</v>
       </c>
       <c r="H61" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I61" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>ROSEMORE ESTS</t>
+          <t>ALDERWOOD RUN</t>
         </is>
       </c>
       <c r="K61" t="n">
-        <v>2093</v>
-      </c>
-      <c r="L61" t="n">
-        <v>10450</v>
-      </c>
+        <v>2169</v>
+      </c>
+      <c r="L61" t="inlineStr"/>
       <c r="M61" t="n">
-        <v>1920</v>
+        <v>2026</v>
       </c>
       <c r="N61" t="n">
-        <v>166</v>
+        <v>38</v>
       </c>
       <c r="O61" t="n">
-        <v>244</v>
-      </c>
-      <c r="P61" t="inlineStr"/>
+        <v>237</v>
+      </c>
+      <c r="P61" t="n">
+        <v>199</v>
+      </c>
       <c r="Q61" t="inlineStr">
         <is>
           <t>Active</t>
@@ -5706,7 +5706,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Chalfont/152-N-Main-St-18914/home/38564500</t>
+          <t>https://www.redfin.com/PA/Royersford/306-East-Sawyer-CT-19468/home/203291145</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
@@ -5716,11 +5716,11 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>PABU2116242</t>
+          <t>PAMC2188890</t>
         </is>
       </c>
       <c r="U61" t="n">
-        <v>510000</v>
+        <v>514987</v>
       </c>
       <c r="V61" t="n">
         <v>0</v>
@@ -5734,17 +5734,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>625 E Walnut St</t>
+          <t>430 Fort Washington Ave</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>North Wales</t>
+          <t>Fort Washington</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -5753,36 +5753,36 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>19454</v>
+        <v>19034</v>
       </c>
       <c r="G62" t="n">
-        <v>514900</v>
+        <v>515000</v>
       </c>
       <c r="H62" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I62" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>North Wales</t>
+          <t>STUART CREEK FARMS</t>
         </is>
       </c>
       <c r="K62" t="n">
-        <v>2520</v>
+        <v>2000</v>
       </c>
       <c r="L62" t="n">
-        <v>6600</v>
+        <v>9466</v>
       </c>
       <c r="M62" t="n">
-        <v>1908</v>
+        <v>1970</v>
       </c>
       <c r="N62" t="n">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="O62" t="n">
-        <v>204</v>
+        <v>258</v>
       </c>
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/North-Wales/625-E-Walnut-St-19454/home/38126535</t>
+          <t>https://www.redfin.com/PA/Fort-Washington/430-Fort-Washington-Ave-19034/home/38893625</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
@@ -5802,11 +5802,11 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>PAMC2191428</t>
+          <t>PAMC2187856</t>
         </is>
       </c>
       <c r="U62" t="n">
-        <v>514900</v>
+        <v>515000</v>
       </c>
       <c r="V62" t="n">
         <v>0</v>
@@ -5825,12 +5825,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>306 East Sawyer Ct</t>
+          <t>134 Easton St</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Royersford</t>
+          <t>Bensalem</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -5839,37 +5839,39 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>19468</v>
+        <v>19020</v>
       </c>
       <c r="G63" t="n">
-        <v>514987</v>
+        <v>519990</v>
       </c>
       <c r="H63" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I63" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>ALDERWOOD RUN</t>
+          <t>WATERSIDE</t>
         </is>
       </c>
       <c r="K63" t="n">
-        <v>2169</v>
-      </c>
-      <c r="L63" t="inlineStr"/>
+        <v>2468</v>
+      </c>
+      <c r="L63" t="n">
+        <v>2583</v>
+      </c>
       <c r="M63" t="n">
-        <v>2026</v>
+        <v>2020</v>
       </c>
       <c r="N63" t="n">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="O63" t="n">
-        <v>237</v>
+        <v>211</v>
       </c>
       <c r="P63" t="n">
-        <v>199</v>
+        <v>265</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -5878,7 +5880,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Royersford/306-East-Sawyer-CT-19468/home/203291145</t>
+          <t>https://www.redfin.com/PA/Bensalem/134-Easton-St-19020/home/174252731</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -5888,11 +5890,11 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>PAMC2188890</t>
+          <t>PABU2124130</t>
         </is>
       </c>
       <c r="U63" t="n">
-        <v>514987</v>
+        <v>519990</v>
       </c>
       <c r="V63" t="n">
         <v>0</v>
@@ -5911,12 +5913,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>430 Fort Washington Ave</t>
+          <t>95 Duane Rd</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Fort Washington</t>
+          <t>Doylestown</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -5925,36 +5927,36 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>19034</v>
+        <v>18901</v>
       </c>
       <c r="G64" t="n">
-        <v>515000</v>
+        <v>524900</v>
       </c>
       <c r="H64" t="n">
         <v>3</v>
       </c>
       <c r="I64" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>STUART CREEK FARMS</t>
+          <t>DUANE VIL</t>
         </is>
       </c>
       <c r="K64" t="n">
-        <v>2000</v>
+        <v>1891</v>
       </c>
       <c r="L64" t="n">
-        <v>9466</v>
+        <v>27520</v>
       </c>
       <c r="M64" t="n">
-        <v>1970</v>
+        <v>1955</v>
       </c>
       <c r="N64" t="n">
-        <v>42</v>
+        <v>86</v>
       </c>
       <c r="O64" t="n">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="P64" t="inlineStr"/>
       <c r="Q64" t="inlineStr">
@@ -5964,7 +5966,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Fort-Washington/430-Fort-Washington-Ave-19034/home/38893625</t>
+          <t>https://www.redfin.com/PA/Doylestown/95-Duane-Rd-18901/home/38587353</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
@@ -5974,11 +5976,11 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>PAMC2187856</t>
+          <t>PABU2122682</t>
         </is>
       </c>
       <c r="U64" t="n">
-        <v>515000</v>
+        <v>524900</v>
       </c>
       <c r="V64" t="n">
         <v>0</v>
@@ -5992,17 +5994,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>134 Easton St</t>
+          <t>510 Sardaro Ln</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Bensalem</t>
+          <t>East Norriton</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -6011,10 +6013,10 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>19020</v>
+        <v>19401</v>
       </c>
       <c r="G65" t="n">
-        <v>519990</v>
+        <v>524999</v>
       </c>
       <c r="H65" t="n">
         <v>4</v>
@@ -6024,27 +6026,25 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>WATERSIDE</t>
+          <t>Norristown</t>
         </is>
       </c>
       <c r="K65" t="n">
-        <v>2468</v>
+        <v>3221</v>
       </c>
       <c r="L65" t="n">
-        <v>2583</v>
+        <v>16012</v>
       </c>
       <c r="M65" t="n">
-        <v>2020</v>
+        <v>1961</v>
       </c>
       <c r="N65" t="n">
-        <v>75</v>
+        <v>13</v>
       </c>
       <c r="O65" t="n">
-        <v>211</v>
-      </c>
-      <c r="P65" t="n">
-        <v>265</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="P65" t="inlineStr"/>
       <c r="Q65" t="inlineStr">
         <is>
           <t>Active</t>
@@ -6052,7 +6052,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Bensalem/134-Easton-St-19020/home/174252731</t>
+          <t>https://www.redfin.com/PA/East-Norriton/510-Sardaro-Ln-19401/home/38332746</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
@@ -6062,11 +6062,11 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>PABU2124130</t>
+          <t>PAMC2190758</t>
         </is>
       </c>
       <c r="U65" t="n">
-        <v>519990</v>
+        <v>524999</v>
       </c>
       <c r="V65" t="n">
         <v>0</v>
@@ -6080,17 +6080,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Single Family Residential</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>95 Duane Rd</t>
+          <t>107 Sidesaddle Way</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Doylestown</t>
+          <t>North Wales</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -6099,46 +6099,48 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>18901</v>
+        <v>19454</v>
       </c>
       <c r="G66" t="n">
-        <v>524900</v>
+        <v>525000</v>
       </c>
       <c r="H66" t="n">
         <v>3</v>
       </c>
       <c r="I66" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>DUANE VIL</t>
+          <t>MONTGOMERY GREENE</t>
         </is>
       </c>
       <c r="K66" t="n">
-        <v>1891</v>
+        <v>2046</v>
       </c>
       <c r="L66" t="n">
-        <v>27520</v>
+        <v>3920</v>
       </c>
       <c r="M66" t="n">
-        <v>1955</v>
+        <v>1995</v>
       </c>
       <c r="N66" t="n">
-        <v>85</v>
+        <v>15</v>
       </c>
       <c r="O66" t="n">
-        <v>278</v>
-      </c>
-      <c r="P66" t="inlineStr"/>
+        <v>257</v>
+      </c>
+      <c r="P66" t="n">
+        <v>202</v>
+      </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Pre On-Market</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Doylestown/95-Duane-Rd-18901/home/38587353</t>
+          <t>https://www.redfin.com/PA/North-Wales/107-Sidesaddle-Way-19454/home/38704943</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
@@ -6148,11 +6150,11 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>PABU2122682</t>
+          <t>PAMC2189208</t>
         </is>
       </c>
       <c r="U66" t="n">
-        <v>524900</v>
+        <v>525000</v>
       </c>
       <c r="V66" t="n">
         <v>0</v>
@@ -6166,17 +6168,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Single Family Residential</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>510 Sardaro Ln</t>
+          <t>140 Lattice Ln</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>East Norriton</t>
+          <t>Collegeville</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6185,38 +6187,40 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>19401</v>
+        <v>19426</v>
       </c>
       <c r="G67" t="n">
-        <v>524999</v>
+        <v>525000</v>
       </c>
       <c r="H67" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I67" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Norristown</t>
+          <t>COURTYARDS</t>
         </is>
       </c>
       <c r="K67" t="n">
-        <v>3221</v>
+        <v>1971</v>
       </c>
       <c r="L67" t="n">
-        <v>16012</v>
+        <v>2400</v>
       </c>
       <c r="M67" t="n">
-        <v>1961</v>
+        <v>2003</v>
       </c>
       <c r="N67" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="O67" t="n">
-        <v>163</v>
-      </c>
-      <c r="P67" t="inlineStr"/>
+        <v>266</v>
+      </c>
+      <c r="P67" t="n">
+        <v>365</v>
+      </c>
       <c r="Q67" t="inlineStr">
         <is>
           <t>Active</t>
@@ -6224,7 +6228,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/East-Norriton/510-Sardaro-Ln-19401/home/38332746</t>
+          <t>https://www.redfin.com/PA/Collegeville/140-Lattice-Ln-19426/home/37950420</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
@@ -6234,11 +6238,11 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>PAMC2190758</t>
+          <t>PAMC2190568</t>
         </is>
       </c>
       <c r="U67" t="n">
-        <v>524999</v>
+        <v>525000</v>
       </c>
       <c r="V67" t="n">
         <v>0</v>
@@ -6257,12 +6261,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>107 Sidesaddle Way</t>
+          <t>98 King St</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>North Wales</t>
+          <t>Bensalem</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6271,7 +6275,7 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>19454</v>
+        <v>19020</v>
       </c>
       <c r="G68" t="n">
         <v>525000</v>
@@ -6280,39 +6284,39 @@
         <v>3</v>
       </c>
       <c r="I68" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>MONTGOMERY GREENE</t>
+          <t>WATERSIDE</t>
         </is>
       </c>
       <c r="K68" t="n">
-        <v>2046</v>
+        <v>2109</v>
       </c>
       <c r="L68" t="n">
-        <v>3920</v>
+        <v>1368</v>
       </c>
       <c r="M68" t="n">
-        <v>1995</v>
+        <v>2023</v>
       </c>
       <c r="N68" t="n">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="O68" t="n">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="P68" t="n">
-        <v>202</v>
+        <v>265</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>Pre On-Market</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/North-Wales/107-Sidesaddle-Way-19454/home/38704943</t>
+          <t>https://www.redfin.com/PA/Bensalem/98-King-St-19020/home/182784224</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -6322,7 +6326,7 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>PAMC2189208</t>
+          <t>PABU2126332</t>
         </is>
       </c>
       <c r="U68" t="n">
@@ -6345,12 +6349,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>140 Lattice Ln</t>
+          <t>27 Addison Ct #2804</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Collegeville</t>
+          <t>Doylestown</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -6359,10 +6363,10 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>19426</v>
+        <v>18901</v>
       </c>
       <c r="G69" t="n">
-        <v>525000</v>
+        <v>529900</v>
       </c>
       <c r="H69" t="n">
         <v>3</v>
@@ -6372,26 +6376,24 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>COURTYARDS</t>
+          <t>DOYLESTOWN STATION</t>
         </is>
       </c>
       <c r="K69" t="n">
-        <v>1971</v>
-      </c>
-      <c r="L69" t="n">
-        <v>2400</v>
-      </c>
+        <v>2086</v>
+      </c>
+      <c r="L69" t="inlineStr"/>
       <c r="M69" t="n">
         <v>2003</v>
       </c>
       <c r="N69" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="O69" t="n">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="P69" t="n">
-        <v>365</v>
+        <v>325</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -6400,7 +6402,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Collegeville/140-Lattice-Ln-19426/home/37950420</t>
+          <t>https://www.redfin.com/PA/Doylestown/27-Addison-Ct-18901/unit-2804/home/181182548</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
@@ -6410,14 +6412,14 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>PAMC2190568</t>
+          <t>PABU2128774</t>
         </is>
       </c>
       <c r="U69" t="n">
-        <v>525000</v>
+        <v>539900</v>
       </c>
       <c r="V69" t="n">
-        <v>0</v>
+        <v>-10000</v>
       </c>
     </row>
     <row r="70">
@@ -6433,12 +6435,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>98 King St</t>
+          <t>0002 Jameson Way Unit BASE STRATFORD INT</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Bensalem</t>
+          <t>Chalfont</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -6447,39 +6449,37 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>19020</v>
+        <v>18914</v>
       </c>
       <c r="G70" t="n">
-        <v>525000</v>
+        <v>529990</v>
       </c>
       <c r="H70" t="n">
         <v>3</v>
       </c>
       <c r="I70" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>WATERSIDE</t>
+          <t>WESTVIEW SQUARE</t>
         </is>
       </c>
       <c r="K70" t="n">
-        <v>2109</v>
-      </c>
-      <c r="L70" t="n">
-        <v>1368</v>
-      </c>
+        <v>1953</v>
+      </c>
+      <c r="L70" t="inlineStr"/>
       <c r="M70" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="N70" t="n">
-        <v>47</v>
+        <v>201</v>
       </c>
       <c r="O70" t="n">
-        <v>249</v>
+        <v>271</v>
       </c>
       <c r="P70" t="n">
-        <v>265</v>
+        <v>167</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Bensalem/98-King-St-19020/home/182784224</t>
+          <t>https://www.redfin.com/PA/Chalfont/0002-Jameson-WAY-18914/unit-BASE-STRATFORD-INT/home/200489764</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
@@ -6498,11 +6498,11 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>PABU2126332</t>
+          <t>PABU2114044</t>
         </is>
       </c>
       <c r="U70" t="n">
-        <v>525000</v>
+        <v>529990</v>
       </c>
       <c r="V70" t="n">
         <v>0</v>
@@ -6511,7 +6511,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>MLS Listing</t>
+          <t>New Construction Plan</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6521,12 +6521,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>27 Addison Ct #2804</t>
+          <t>Stratford Plan</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Doylestown</t>
+          <t>Chalfont</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -6535,10 +6535,10 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>18901</v>
+        <v>18914</v>
       </c>
       <c r="G71" t="n">
-        <v>529900</v>
+        <v>529990</v>
       </c>
       <c r="H71" t="n">
         <v>3</v>
@@ -6548,24 +6548,22 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>DOYLESTOWN STATION</t>
+          <t>Chalfont</t>
         </is>
       </c>
       <c r="K71" t="n">
-        <v>2086</v>
+        <v>1953</v>
       </c>
       <c r="L71" t="inlineStr"/>
-      <c r="M71" t="n">
-        <v>2003</v>
-      </c>
+      <c r="M71" t="inlineStr"/>
       <c r="N71" t="n">
-        <v>20</v>
+        <v>203</v>
       </c>
       <c r="O71" t="n">
-        <v>254</v>
+        <v>271</v>
       </c>
       <c r="P71" t="n">
-        <v>325</v>
+        <v>167</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -6574,24 +6572,24 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Doylestown/27-Addison-Ct-18901/unit-2804/home/181182548</t>
+          <t>https://www.redfin.com/PA/Chalfont/Chalfont/Stratford/home/200417068</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>BRIGHT MLS</t>
+          <t>Zillow</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>PABU2128774</t>
+          <t>C24C65EA8D34</t>
         </is>
       </c>
       <c r="U71" t="n">
-        <v>539900</v>
+        <v>529990</v>
       </c>
       <c r="V71" t="n">
-        <v>-10000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -6607,12 +6605,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>0002 Jameson Way Unit BASE STRATFORD INT</t>
+          <t>178 Pinecrest Ln</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Chalfont</t>
+          <t>Lansdale</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -6621,10 +6619,10 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>18914</v>
+        <v>19446</v>
       </c>
       <c r="G72" t="n">
-        <v>529990</v>
+        <v>534900</v>
       </c>
       <c r="H72" t="n">
         <v>3</v>
@@ -6634,24 +6632,26 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>WESTVIEW SQUARE</t>
+          <t>PINE CREST</t>
         </is>
       </c>
       <c r="K72" t="n">
-        <v>1953</v>
-      </c>
-      <c r="L72" t="inlineStr"/>
+        <v>2126</v>
+      </c>
+      <c r="L72" t="n">
+        <v>3384</v>
+      </c>
       <c r="M72" t="n">
-        <v>2026</v>
+        <v>1990</v>
       </c>
       <c r="N72" t="n">
-        <v>200</v>
+        <v>5</v>
       </c>
       <c r="O72" t="n">
-        <v>271</v>
+        <v>252</v>
       </c>
       <c r="P72" t="n">
-        <v>167</v>
+        <v>236</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -6660,7 +6660,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Chalfont/0002-Jameson-WAY-18914/unit-BASE-STRATFORD-INT/home/200489764</t>
+          <t>https://www.redfin.com/PA/Lansdale/178-Pinecrest-Ln-19446/home/38703417</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
@@ -6670,11 +6670,11 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>PABU2114044</t>
+          <t>PAMC2192488</t>
         </is>
       </c>
       <c r="U72" t="n">
-        <v>529990</v>
+        <v>534900</v>
       </c>
       <c r="V72" t="n">
         <v>0</v>
@@ -6688,17 +6688,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>178 Pinecrest Ln</t>
+          <t>2924 June Ave</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Lansdale</t>
+          <t>Bensalem</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -6707,7 +6707,7 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>19446</v>
+        <v>19020</v>
       </c>
       <c r="G73" t="n">
         <v>534900</v>
@@ -6716,31 +6716,29 @@
         <v>3</v>
       </c>
       <c r="I73" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>PINE CREST</t>
+          <t>Bensalem</t>
         </is>
       </c>
       <c r="K73" t="n">
-        <v>2126</v>
+        <v>1931</v>
       </c>
       <c r="L73" t="n">
-        <v>3384</v>
+        <v>15625</v>
       </c>
       <c r="M73" t="n">
-        <v>1990</v>
+        <v>1927</v>
       </c>
       <c r="N73" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O73" t="n">
-        <v>252</v>
-      </c>
-      <c r="P73" t="n">
-        <v>236</v>
-      </c>
+        <v>277</v>
+      </c>
+      <c r="P73" t="inlineStr"/>
       <c r="Q73" t="inlineStr">
         <is>
           <t>Active</t>
@@ -6748,7 +6746,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Lansdale/178-Pinecrest-Ln-19446/home/38703417</t>
+          <t>https://www.redfin.com/PA/Bensalem/2924-June-Ave-19020/home/38391429</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
@@ -6758,7 +6756,7 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>PAMC2192488</t>
+          <t>PABU2129946</t>
         </is>
       </c>
       <c r="U73" t="n">
@@ -6781,12 +6779,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2924 June Ave</t>
+          <t>1289 Meadowview Dr</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Bensalem</t>
+          <t>Pottstown</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -6795,36 +6793,36 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>19020</v>
+        <v>19464</v>
       </c>
       <c r="G74" t="n">
-        <v>534900</v>
+        <v>535000</v>
       </c>
       <c r="H74" t="n">
         <v>3</v>
       </c>
       <c r="I74" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Bensalem</t>
+          <t>TURNBERRY FARM</t>
         </is>
       </c>
       <c r="K74" t="n">
-        <v>1931</v>
+        <v>2288</v>
       </c>
       <c r="L74" t="n">
-        <v>15625</v>
+        <v>10006</v>
       </c>
       <c r="M74" t="n">
-        <v>1927</v>
+        <v>1999</v>
       </c>
       <c r="N74" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O74" t="n">
-        <v>277</v>
+        <v>234</v>
       </c>
       <c r="P74" t="inlineStr"/>
       <c r="Q74" t="inlineStr">
@@ -6834,7 +6832,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Bensalem/2924-June-Ave-19020/home/38391429</t>
+          <t>https://www.redfin.com/PA/Pottstown/1289-Meadowview-Dr-19464/home/39030041</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
@@ -6844,11 +6842,11 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>PABU2129946</t>
+          <t>PAMC2191992</t>
         </is>
       </c>
       <c r="U74" t="n">
-        <v>534900</v>
+        <v>535000</v>
       </c>
       <c r="V74" t="n">
         <v>0</v>
@@ -6867,12 +6865,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>1289 Meadowview Dr</t>
+          <t>321 Almshouse Rd</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Pottstown</t>
+          <t>Richboro</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -6881,36 +6879,36 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>19464</v>
+        <v>18954</v>
       </c>
       <c r="G75" t="n">
-        <v>535000</v>
+        <v>539000</v>
       </c>
       <c r="H75" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I75" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>TURNBERRY FARM</t>
+          <t>Richboro</t>
         </is>
       </c>
       <c r="K75" t="n">
-        <v>2288</v>
+        <v>1898</v>
       </c>
       <c r="L75" t="n">
-        <v>10006</v>
+        <v>21800</v>
       </c>
       <c r="M75" t="n">
-        <v>1999</v>
+        <v>1946</v>
       </c>
       <c r="N75" t="n">
-        <v>6</v>
+        <v>68</v>
       </c>
       <c r="O75" t="n">
-        <v>234</v>
+        <v>284</v>
       </c>
       <c r="P75" t="inlineStr"/>
       <c r="Q75" t="inlineStr">
@@ -6920,7 +6918,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Pottstown/1289-Meadowview-Dr-19464/home/39030041</t>
+          <t>https://www.redfin.com/PA/Richboro/321-Almshouse-Rd-18954/home/38973699</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
@@ -6930,11 +6928,11 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>PAMC2191992</t>
+          <t>PABU2124922</t>
         </is>
       </c>
       <c r="U75" t="n">
-        <v>535000</v>
+        <v>539000</v>
       </c>
       <c r="V75" t="n">
         <v>0</v>
@@ -6953,12 +6951,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>321 Almshouse Rd</t>
+          <t>716 Springdell Rd</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Richboro</t>
+          <t>King Of Prussia</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -6967,36 +6965,36 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>18954</v>
+        <v>19406</v>
       </c>
       <c r="G76" t="n">
-        <v>539000</v>
+        <v>539900</v>
       </c>
       <c r="H76" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I76" t="n">
         <v>2</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Richboro</t>
+          <t>King of Prussia</t>
         </is>
       </c>
       <c r="K76" t="n">
-        <v>1898</v>
+        <v>1890</v>
       </c>
       <c r="L76" t="n">
-        <v>21800</v>
+        <v>8100</v>
       </c>
       <c r="M76" t="n">
-        <v>1946</v>
+        <v>1966</v>
       </c>
       <c r="N76" t="n">
-        <v>67</v>
+        <v>7</v>
       </c>
       <c r="O76" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="P76" t="inlineStr"/>
       <c r="Q76" t="inlineStr">
@@ -7006,7 +7004,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Richboro/321-Almshouse-Rd-18954/home/38973699</t>
+          <t>https://www.redfin.com/PA/King-of-Prussia/716-Springdell-Rd-19406/home/38984458</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
@@ -7016,11 +7014,11 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>PABU2124922</t>
+          <t>PAMC2192216</t>
         </is>
       </c>
       <c r="U76" t="n">
-        <v>539000</v>
+        <v>539900</v>
       </c>
       <c r="V76" t="n">
         <v>0</v>
@@ -7034,17 +7032,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Single Family Residential</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>716 Springdell Rd</t>
+          <t>112 Federal St</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>King Of Prussia</t>
+          <t>Bensalem</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -7053,7 +7051,7 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>19406</v>
+        <v>19020</v>
       </c>
       <c r="G77" t="n">
         <v>539900</v>
@@ -7062,29 +7060,29 @@
         <v>3</v>
       </c>
       <c r="I77" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>King of Prussia</t>
+          <t>WATERSIDE</t>
         </is>
       </c>
       <c r="K77" t="n">
-        <v>1890</v>
-      </c>
-      <c r="L77" t="n">
-        <v>8100</v>
-      </c>
+        <v>2178</v>
+      </c>
+      <c r="L77" t="inlineStr"/>
       <c r="M77" t="n">
-        <v>1966</v>
+        <v>2016</v>
       </c>
       <c r="N77" t="n">
-        <v>6</v>
+        <v>75</v>
       </c>
       <c r="O77" t="n">
-        <v>286</v>
-      </c>
-      <c r="P77" t="inlineStr"/>
+        <v>248</v>
+      </c>
+      <c r="P77" t="n">
+        <v>265</v>
+      </c>
       <c r="Q77" t="inlineStr">
         <is>
           <t>Active</t>
@@ -7092,7 +7090,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/King-of-Prussia/716-Springdell-Rd-19406/home/38984458</t>
+          <t>https://www.redfin.com/PA/Bensalem/112-Federal-St-19020/home/69367667</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
@@ -7102,7 +7100,7 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>PAMC2192216</t>
+          <t>PABU2124156</t>
         </is>
       </c>
       <c r="U77" t="n">
@@ -7120,17 +7118,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>112 Federal St</t>
+          <t>703 Evansburg Rd</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Bensalem</t>
+          <t>Collegeville</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -7139,38 +7137,38 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>19020</v>
+        <v>19426</v>
       </c>
       <c r="G78" t="n">
-        <v>539900</v>
+        <v>540000</v>
       </c>
       <c r="H78" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I78" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>WATERSIDE</t>
+          <t>Collegeville</t>
         </is>
       </c>
       <c r="K78" t="n">
-        <v>2178</v>
-      </c>
-      <c r="L78" t="inlineStr"/>
+        <v>2596</v>
+      </c>
+      <c r="L78" t="n">
+        <v>33200</v>
+      </c>
       <c r="M78" t="n">
-        <v>2016</v>
+        <v>1850</v>
       </c>
       <c r="N78" t="n">
-        <v>74</v>
+        <v>15</v>
       </c>
       <c r="O78" t="n">
-        <v>248</v>
-      </c>
-      <c r="P78" t="n">
-        <v>265</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="P78" t="inlineStr"/>
       <c r="Q78" t="inlineStr">
         <is>
           <t>Active</t>
@@ -7178,7 +7176,7 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Bensalem/112-Federal-St-19020/home/69367667</t>
+          <t>https://www.redfin.com/PA/Collegeville/703-Evansburg-Rd-19426/home/38802205</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
@@ -7188,14 +7186,14 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>PABU2124156</t>
+          <t>PAMC2190248</t>
         </is>
       </c>
       <c r="U78" t="n">
-        <v>539900</v>
+        <v>550000</v>
       </c>
       <c r="V78" t="n">
-        <v>0</v>
+        <v>-10000</v>
       </c>
     </row>
     <row r="79">
@@ -7206,12 +7204,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Single Family Residential</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>703 Evansburg Rd</t>
+          <t>160 Lattice Ln</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -7228,43 +7226,45 @@
         <v>19426</v>
       </c>
       <c r="G79" t="n">
-        <v>540000</v>
+        <v>545000</v>
       </c>
       <c r="H79" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I79" t="n">
         <v>2</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Collegeville</t>
+          <t>COURTYARDS</t>
         </is>
       </c>
       <c r="K79" t="n">
-        <v>2596</v>
+        <v>2113</v>
       </c>
       <c r="L79" t="n">
-        <v>33200</v>
+        <v>2400</v>
       </c>
       <c r="M79" t="n">
-        <v>1850</v>
+        <v>2003</v>
       </c>
       <c r="N79" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="O79" t="n">
-        <v>208</v>
-      </c>
-      <c r="P79" t="inlineStr"/>
+        <v>258</v>
+      </c>
+      <c r="P79" t="n">
+        <v>365</v>
+      </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Pre On-Market</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Collegeville/703-Evansburg-Rd-19426/home/38802205</t>
+          <t>https://www.redfin.com/PA/Collegeville/160-Lattice-Ln-19426/home/37950430</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
@@ -7274,14 +7274,14 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>PAMC2190248</t>
+          <t>PAMC2188142</t>
         </is>
       </c>
       <c r="U79" t="n">
-        <v>550000</v>
+        <v>545000</v>
       </c>
       <c r="V79" t="n">
-        <v>-10000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -7292,17 +7292,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>160 Lattice Ln</t>
+          <t>265 Haven Dr</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Collegeville</t>
+          <t>Pottstown</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -7311,48 +7311,48 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>19426</v>
+        <v>19464</v>
       </c>
       <c r="G80" t="n">
-        <v>545000</v>
+        <v>547975</v>
       </c>
       <c r="H80" t="n">
+        <v>4</v>
+      </c>
+      <c r="I80" t="n">
         <v>3</v>
       </c>
-      <c r="I80" t="n">
-        <v>2</v>
-      </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>COURTYARDS</t>
+          <t>POTTSGROVE HUNT</t>
         </is>
       </c>
       <c r="K80" t="n">
-        <v>2113</v>
+        <v>2613</v>
       </c>
       <c r="L80" t="n">
-        <v>2400</v>
+        <v>8766</v>
       </c>
       <c r="M80" t="n">
-        <v>2003</v>
+        <v>2024</v>
       </c>
       <c r="N80" t="n">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="O80" t="n">
-        <v>258</v>
+        <v>210</v>
       </c>
       <c r="P80" t="n">
-        <v>365</v>
+        <v>307</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>Pre On-Market</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Collegeville/160-Lattice-Ln-19426/home/37950430</t>
+          <t>https://www.redfin.com/PA/Pottstown/265-Haven-Dr-19464/home/184543784</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
@@ -7362,11 +7362,11 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>PAMC2188142</t>
+          <t>PAMC2187804</t>
         </is>
       </c>
       <c r="U80" t="n">
-        <v>545000</v>
+        <v>547975</v>
       </c>
       <c r="V80" t="n">
         <v>0</v>
@@ -7385,12 +7385,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>265 Haven Dr</t>
+          <t>311 Spring Ln</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Pottstown</t>
+          <t>King Of Prussia</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -7399,40 +7399,38 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>19464</v>
+        <v>19406</v>
       </c>
       <c r="G81" t="n">
-        <v>547975</v>
+        <v>549000</v>
       </c>
       <c r="H81" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I81" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>POTTSGROVE HUNT</t>
+          <t>MERION VIEW</t>
         </is>
       </c>
       <c r="K81" t="n">
-        <v>2613</v>
+        <v>2017</v>
       </c>
       <c r="L81" t="n">
-        <v>8766</v>
+        <v>10400</v>
       </c>
       <c r="M81" t="n">
-        <v>2024</v>
+        <v>1956</v>
       </c>
       <c r="N81" t="n">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="O81" t="n">
-        <v>210</v>
-      </c>
-      <c r="P81" t="n">
-        <v>307</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="P81" t="inlineStr"/>
       <c r="Q81" t="inlineStr">
         <is>
           <t>Active</t>
@@ -7440,7 +7438,7 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Pottstown/265-Haven-Dr-19464/home/184543784</t>
+          <t>https://www.redfin.com/PA/King-of-Prussia/311-Spring-Ln-19406/home/38984387</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
@@ -7450,11 +7448,11 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>PAMC2187804</t>
+          <t>PAMC2191836</t>
         </is>
       </c>
       <c r="U81" t="n">
-        <v>547975</v>
+        <v>549000</v>
       </c>
       <c r="V81" t="n">
         <v>0</v>
@@ -7473,12 +7471,12 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>311 Spring Ln</t>
+          <t>216 Upper Stump Rd</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>King Of Prussia</t>
+          <t>Chalfont</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -7487,7 +7485,7 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>19406</v>
+        <v>18914</v>
       </c>
       <c r="G82" t="n">
         <v>549000</v>
@@ -7500,23 +7498,23 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>MERION VIEW</t>
+          <t>Chalfont</t>
         </is>
       </c>
       <c r="K82" t="n">
-        <v>2017</v>
+        <v>1992</v>
       </c>
       <c r="L82" t="n">
-        <v>10400</v>
+        <v>30900</v>
       </c>
       <c r="M82" t="n">
-        <v>1956</v>
+        <v>1965</v>
       </c>
       <c r="N82" t="n">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="O82" t="n">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="P82" t="inlineStr"/>
       <c r="Q82" t="inlineStr">
@@ -7526,7 +7524,7 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/King-of-Prussia/311-Spring-Ln-19406/home/38984387</t>
+          <t>https://www.redfin.com/PA/Chalfont/216-Upper-Stump-Rd-18914/home/38913664</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
@@ -7536,7 +7534,7 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>PAMC2191836</t>
+          <t>PABU2122106</t>
         </is>
       </c>
       <c r="U82" t="n">
@@ -7554,17 +7552,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Single Family Residential</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>216 Upper Stump Rd</t>
+          <t>535 Bullock Ave #1</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Chalfont</t>
+          <t>Conshohocken</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -7573,38 +7571,40 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>18914</v>
+        <v>19428</v>
       </c>
       <c r="G83" t="n">
-        <v>549000</v>
+        <v>549900</v>
       </c>
       <c r="H83" t="n">
         <v>3</v>
       </c>
       <c r="I83" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Chalfont</t>
+          <t>MATSONFORD COMMONS</t>
         </is>
       </c>
       <c r="K83" t="n">
         <v>1992</v>
       </c>
       <c r="L83" t="n">
-        <v>30900</v>
+        <v>1920</v>
       </c>
       <c r="M83" t="n">
-        <v>1965</v>
+        <v>1994</v>
       </c>
       <c r="N83" t="n">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="O83" t="n">
         <v>276</v>
       </c>
-      <c r="P83" t="inlineStr"/>
+      <c r="P83" t="n">
+        <v>215</v>
+      </c>
       <c r="Q83" t="inlineStr">
         <is>
           <t>Active</t>
@@ -7612,7 +7612,7 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Chalfont/216-Upper-Stump-Rd-18914/home/38913664</t>
+          <t>https://www.redfin.com/PA/Conshohocken/535-Bullock-St-19428/unit-1/home/38194844</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
@@ -7622,11 +7622,11 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>PABU2122106</t>
+          <t>PAMC2184768</t>
         </is>
       </c>
       <c r="U83" t="n">
-        <v>549000</v>
+        <v>549900</v>
       </c>
       <c r="V83" t="n">
         <v>0</v>
@@ -7645,12 +7645,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>535 Bullock Ave #1</t>
+          <t>210 Polo Dr</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Conshohocken</t>
+          <t>North Wales</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -7659,7 +7659,7 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>19428</v>
+        <v>19454</v>
       </c>
       <c r="G84" t="n">
         <v>549900</v>
@@ -7672,26 +7672,26 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>MATSONFORD COMMONS</t>
+          <t>MONTGOMERY GREENE</t>
         </is>
       </c>
       <c r="K84" t="n">
+        <v>2288</v>
+      </c>
+      <c r="L84" t="n">
+        <v>6670</v>
+      </c>
+      <c r="M84" t="n">
         <v>1992</v>
       </c>
-      <c r="L84" t="n">
-        <v>1920</v>
-      </c>
-      <c r="M84" t="n">
-        <v>1994</v>
-      </c>
       <c r="N84" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="O84" t="n">
-        <v>276</v>
+        <v>240</v>
       </c>
       <c r="P84" t="n">
-        <v>215</v>
+        <v>150</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -7700,7 +7700,7 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Conshohocken/535-Bullock-St-19428/unit-1/home/38194844</t>
+          <t>https://www.redfin.com/PA/North-Wales/210-Polo-Dr-19454/home/38700704</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
@@ -7710,7 +7710,7 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>PAMC2184768</t>
+          <t>PAMC2189534</t>
         </is>
       </c>
       <c r="U84" t="n">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>210 Polo Dr</t>
+          <t>4040 Diane Way</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>North Wales</t>
+          <t>Doylestown</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -7747,7 +7747,7 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>19454</v>
+        <v>18902</v>
       </c>
       <c r="G85" t="n">
         <v>549900</v>
@@ -7760,26 +7760,26 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>MONTGOMERY GREENE</t>
+          <t>FIELDSTONE PLACE</t>
         </is>
       </c>
       <c r="K85" t="n">
-        <v>2288</v>
+        <v>2046</v>
       </c>
       <c r="L85" t="n">
-        <v>6670</v>
+        <v>5516</v>
       </c>
       <c r="M85" t="n">
-        <v>1992</v>
+        <v>1996</v>
       </c>
       <c r="N85" t="n">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="O85" t="n">
-        <v>240</v>
+        <v>269</v>
       </c>
       <c r="P85" t="n">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -7788,7 +7788,7 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/North-Wales/210-Polo-Dr-19454/home/38700704</t>
+          <t>https://www.redfin.com/PA/Doylestown/4040-Diane-Way-18902/home/38554347</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
@@ -7798,7 +7798,7 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>PAMC2189534</t>
+          <t>PABU2124804</t>
         </is>
       </c>
       <c r="U85" t="n">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>4040 Diane Way</t>
+          <t>0001 Jameson Way Unit BASE WARWICK INT</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Doylestown</t>
+          <t>Chalfont</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -7835,10 +7835,10 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>18902</v>
+        <v>18914</v>
       </c>
       <c r="G86" t="n">
-        <v>549900</v>
+        <v>549990</v>
       </c>
       <c r="H86" t="n">
         <v>3</v>
@@ -7848,26 +7848,24 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>FIELDSTONE PLACE</t>
+          <t>WESTVIEW SQUARE</t>
         </is>
       </c>
       <c r="K86" t="n">
-        <v>2046</v>
-      </c>
-      <c r="L86" t="n">
-        <v>5516</v>
-      </c>
+        <v>2335</v>
+      </c>
+      <c r="L86" t="inlineStr"/>
       <c r="M86" t="n">
-        <v>1996</v>
+        <v>2026</v>
       </c>
       <c r="N86" t="n">
-        <v>69</v>
+        <v>201</v>
       </c>
       <c r="O86" t="n">
-        <v>269</v>
+        <v>236</v>
       </c>
       <c r="P86" t="n">
-        <v>25</v>
+        <v>167</v>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
@@ -7876,7 +7874,7 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Doylestown/4040-Diane-Way-18902/home/38554347</t>
+          <t>https://www.redfin.com/PA/Chalfont/0001-Jameson-WAY-18914/unit-BASE-WARWICK-INT/home/200489640</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
@@ -7886,11 +7884,11 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>PABU2124804</t>
+          <t>PABU2114036</t>
         </is>
       </c>
       <c r="U86" t="n">
-        <v>549900</v>
+        <v>549990</v>
       </c>
       <c r="V86" t="n">
         <v>0</v>
@@ -7899,7 +7897,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>MLS Listing</t>
+          <t>New Construction Plan</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7909,7 +7907,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>0001 Jameson Way Unit BASE WARWICK INT</t>
+          <t>Warwick Plan</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -7936,18 +7934,16 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>WESTVIEW SQUARE</t>
+          <t>Chalfont</t>
         </is>
       </c>
       <c r="K87" t="n">
         <v>2335</v>
       </c>
       <c r="L87" t="inlineStr"/>
-      <c r="M87" t="n">
-        <v>2026</v>
-      </c>
+      <c r="M87" t="inlineStr"/>
       <c r="N87" t="n">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="O87" t="n">
         <v>236</v>
@@ -7962,17 +7958,17 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Chalfont/0001-Jameson-WAY-18914/unit-BASE-WARWICK-INT/home/200489640</t>
+          <t>https://www.redfin.com/PA/Chalfont/Chalfont/Warwick/home/200417066</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>BRIGHT MLS</t>
+          <t>Zillow</t>
         </is>
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>PABU2114036</t>
+          <t>1C26E40E380D</t>
         </is>
       </c>
       <c r="U87" t="n">
@@ -8035,7 +8031,7 @@
         <v>1961</v>
       </c>
       <c r="N88" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O88" t="n">
         <v>304</v>
@@ -8119,7 +8115,7 @@
         <v>2017</v>
       </c>
       <c r="N89" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O89" t="n">
         <v>261</v>
@@ -8207,7 +8203,7 @@
         <v>1984</v>
       </c>
       <c r="N90" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O90" t="n">
         <v>286</v>
@@ -8293,7 +8289,7 @@
         <v>1979</v>
       </c>
       <c r="N91" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O91" t="n">
         <v>241</v>
@@ -8379,7 +8375,7 @@
         <v>1965</v>
       </c>
       <c r="N92" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="O92" t="n">
         <v>270</v>
@@ -8465,7 +8461,7 @@
         <v>2011</v>
       </c>
       <c r="N93" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O93" t="n">
         <v>246</v>
@@ -8553,7 +8549,7 @@
         <v>2026</v>
       </c>
       <c r="N94" t="n">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="O94" t="n">
         <v>285</v>
@@ -8641,7 +8637,7 @@
         <v>2026</v>
       </c>
       <c r="N95" t="n">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="O95" t="n">
         <v>285</v>
@@ -8727,7 +8723,7 @@
         <v>1987</v>
       </c>
       <c r="N96" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O96" t="n">
         <v>181</v>
@@ -8811,7 +8807,7 @@
         <v>1974</v>
       </c>
       <c r="N97" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O97" t="n">
         <v>288</v>
@@ -8983,7 +8979,7 @@
         <v>2003</v>
       </c>
       <c r="N99" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="O99" t="n">
         <v>273</v>
@@ -9071,7 +9067,7 @@
         <v>1956</v>
       </c>
       <c r="N100" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O100" t="n">
         <v>210</v>
@@ -9157,7 +9153,7 @@
         <v>2026</v>
       </c>
       <c r="N101" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O101" t="n">
         <v>224</v>
@@ -9245,7 +9241,7 @@
         <v>2023</v>
       </c>
       <c r="N102" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O102" t="n">
         <v>282</v>
@@ -9333,7 +9329,7 @@
         <v>2026</v>
       </c>
       <c r="N103" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O103" t="n">
         <v>242</v>
@@ -9419,7 +9415,7 @@
         <v>2021</v>
       </c>
       <c r="N104" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O104" t="n">
         <v>159</v>
@@ -9507,7 +9503,7 @@
         <v>1964</v>
       </c>
       <c r="N105" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O105" t="n">
         <v>288</v>
@@ -9593,7 +9589,7 @@
         <v>1990</v>
       </c>
       <c r="N106" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O106" t="n">
         <v>224</v>
@@ -9679,7 +9675,7 @@
         <v>1982</v>
       </c>
       <c r="N107" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O107" t="n">
         <v>253</v>
@@ -9765,7 +9761,7 @@
         <v>1967</v>
       </c>
       <c r="N108" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O108" t="n">
         <v>247</v>
@@ -9851,7 +9847,7 @@
         <v>2023</v>
       </c>
       <c r="N109" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="O109" t="n">
         <v>248</v>
@@ -9937,7 +9933,7 @@
         <v>2026</v>
       </c>
       <c r="N110" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O110" t="n">
         <v>255</v>
@@ -10023,7 +10019,7 @@
         <v>2026</v>
       </c>
       <c r="N111" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="O111" t="n">
         <v>301</v>
@@ -10111,7 +10107,7 @@
         <v>1969</v>
       </c>
       <c r="N112" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O112" t="n">
         <v>285</v>
@@ -10152,17 +10148,17 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Single Family Residential</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>51 Jenkins Ave</t>
+          <t>342 Ridgewood Dr</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Lansdale</t>
+          <t>Royersford</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -10171,38 +10167,40 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>19446</v>
+        <v>19468</v>
       </c>
       <c r="G113" t="n">
         <v>589900</v>
       </c>
       <c r="H113" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I113" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Lansdale</t>
+          <t>ENCLAVE @ RIDGEWOOD</t>
         </is>
       </c>
       <c r="K113" t="n">
-        <v>1853</v>
+        <v>2731</v>
       </c>
       <c r="L113" t="n">
-        <v>5840</v>
+        <v>998</v>
       </c>
       <c r="M113" t="n">
-        <v>1918</v>
+        <v>2021</v>
       </c>
       <c r="N113" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O113" t="n">
-        <v>318</v>
-      </c>
-      <c r="P113" t="inlineStr"/>
+        <v>216</v>
+      </c>
+      <c r="P113" t="n">
+        <v>204</v>
+      </c>
       <c r="Q113" t="inlineStr">
         <is>
           <t>Active</t>
@@ -10210,7 +10208,7 @@
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Lansdale/51-Jenkins-Ave-19446/home/38080425</t>
+          <t>https://www.redfin.com/PA/Royersford/342-Ridgewood-Dr-19468/home/174506881</t>
         </is>
       </c>
       <c r="S113" t="inlineStr">
@@ -10220,7 +10218,7 @@
       </c>
       <c r="T113" t="inlineStr">
         <is>
-          <t>PAMC2192094</t>
+          <t>PAMC2187224</t>
         </is>
       </c>
       <c r="U113" t="n">
@@ -10238,17 +10236,17 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>342 Ridgewood Dr</t>
+          <t>51 Jenkins Ave</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Royersford</t>
+          <t>Lansdale</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -10257,48 +10255,46 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>19468</v>
+        <v>19446</v>
       </c>
       <c r="G114" t="n">
         <v>589900</v>
       </c>
       <c r="H114" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I114" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>ENCLAVE @ RIDGEWOOD</t>
+          <t>Lansdale</t>
         </is>
       </c>
       <c r="K114" t="n">
-        <v>2731</v>
+        <v>1853</v>
       </c>
       <c r="L114" t="n">
-        <v>998</v>
+        <v>5840</v>
       </c>
       <c r="M114" t="n">
-        <v>2021</v>
+        <v>1918</v>
       </c>
       <c r="N114" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="O114" t="n">
-        <v>216</v>
-      </c>
-      <c r="P114" t="n">
-        <v>204</v>
-      </c>
+        <v>318</v>
+      </c>
+      <c r="P114" t="inlineStr"/>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>Pre On-Market</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Royersford/342-Ridgewood-Dr-19468/home/174506881</t>
+          <t>https://www.redfin.com/PA/Lansdale/51-Jenkins-Ave-19446/home/38080425</t>
         </is>
       </c>
       <c r="S114" t="inlineStr">
@@ -10308,7 +10304,7 @@
       </c>
       <c r="T114" t="inlineStr">
         <is>
-          <t>PAMC2187224</t>
+          <t>PAMC2192094</t>
         </is>
       </c>
       <c r="U114" t="n">
@@ -10371,7 +10367,7 @@
         <v>2019</v>
       </c>
       <c r="N115" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O115" t="n">
         <v>267</v>
@@ -10459,7 +10455,7 @@
         <v>2022</v>
       </c>
       <c r="N116" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O116" t="n">
         <v>191</v>
@@ -10547,7 +10543,7 @@
         <v>1971</v>
       </c>
       <c r="N117" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O117" t="n">
         <v>308</v>
@@ -10633,7 +10629,7 @@
         <v>1965</v>
       </c>
       <c r="N118" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O118" t="n">
         <v>183</v>
@@ -10719,7 +10715,7 @@
         <v>2018</v>
       </c>
       <c r="N119" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O119" t="n">
         <v>270</v>
@@ -10805,7 +10801,7 @@
         <v>2026</v>
       </c>
       <c r="N120" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O120" t="n">
         <v>274</v>
@@ -10873,7 +10869,7 @@
         <v>599000</v>
       </c>
       <c r="H121" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I121" t="n">
         <v>1.5</v>
@@ -10893,7 +10889,7 @@
         <v>1955</v>
       </c>
       <c r="N121" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O121" t="n">
         <v>324</v>
@@ -10979,7 +10975,7 @@
         <v>1997</v>
       </c>
       <c r="N122" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O122" t="n">
         <v>221</v>
@@ -11065,7 +11061,7 @@
         <v>2026</v>
       </c>
       <c r="N123" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O123" t="n">
         <v>271</v>
@@ -11149,7 +11145,7 @@
         <v>2026</v>
       </c>
       <c r="N124" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O124" t="n">
         <v>271</v>
@@ -11195,7 +11191,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>224 Upper Valley Rd</t>
+          <t>128 Weber Rd</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -11222,33 +11218,33 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>MERRYBROOK</t>
+          <t>PENN BROOKE</t>
         </is>
       </c>
       <c r="K125" t="n">
-        <v>1810</v>
+        <v>1852</v>
       </c>
       <c r="L125" t="n">
-        <v>15120</v>
+        <v>32400</v>
       </c>
       <c r="M125" t="n">
-        <v>1957</v>
+        <v>1969</v>
       </c>
       <c r="N125" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="O125" t="n">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="P125" t="inlineStr"/>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Pre On-Market</t>
         </is>
       </c>
       <c r="R125" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/North-Wales/224-Upper-Valley-Rd-19454/home/38946036</t>
+          <t>https://www.redfin.com/PA/North-Wales/128-Weber-Rd-19454/home/38946094</t>
         </is>
       </c>
       <c r="S125" t="inlineStr">
@@ -11258,7 +11254,7 @@
       </c>
       <c r="T125" t="inlineStr">
         <is>
-          <t>PAMC2189714</t>
+          <t>PAMC2193162</t>
         </is>
       </c>
       <c r="U125" t="n">
@@ -11281,12 +11277,12 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>529 Faith Dr</t>
+          <t>224 Upper Valley Rd</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>East Norriton</t>
+          <t>North Wales</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -11295,7 +11291,7 @@
         </is>
       </c>
       <c r="F126" t="n">
-        <v>19403</v>
+        <v>19454</v>
       </c>
       <c r="G126" t="n">
         <v>599900</v>
@@ -11308,23 +11304,23 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>Eagleville</t>
+          <t>MERRYBROOK</t>
         </is>
       </c>
       <c r="K126" t="n">
-        <v>2903</v>
+        <v>1810</v>
       </c>
       <c r="L126" t="n">
-        <v>23043</v>
+        <v>15120</v>
       </c>
       <c r="M126" t="n">
-        <v>1986</v>
+        <v>1957</v>
       </c>
       <c r="N126" t="n">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="O126" t="n">
-        <v>207</v>
+        <v>331</v>
       </c>
       <c r="P126" t="inlineStr"/>
       <c r="Q126" t="inlineStr">
@@ -11334,7 +11330,7 @@
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/East-Norriton/529-Faith-Dr-19403/home/38324099</t>
+          <t>https://www.redfin.com/PA/North-Wales/224-Upper-Valley-Rd-19454/home/38946036</t>
         </is>
       </c>
       <c r="S126" t="inlineStr">
@@ -11344,7 +11340,7 @@
       </c>
       <c r="T126" t="inlineStr">
         <is>
-          <t>PAMC2187382</t>
+          <t>PAMC2189714</t>
         </is>
       </c>
       <c r="U126" t="n">
@@ -11367,12 +11363,12 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>361 Spring Garden St</t>
+          <t>529 Faith Dr</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Conshohocken</t>
+          <t>East Norriton</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -11381,36 +11377,36 @@
         </is>
       </c>
       <c r="F127" t="n">
-        <v>19428</v>
+        <v>19403</v>
       </c>
       <c r="G127" t="n">
         <v>599900</v>
       </c>
       <c r="H127" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I127" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>MERION HILL</t>
+          <t>Eagleville</t>
         </is>
       </c>
       <c r="K127" t="n">
-        <v>2650</v>
+        <v>2903</v>
       </c>
       <c r="L127" t="n">
-        <v>23958</v>
+        <v>23043</v>
       </c>
       <c r="M127" t="n">
-        <v>1956</v>
+        <v>1986</v>
       </c>
       <c r="N127" t="n">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="O127" t="n">
-        <v>226</v>
+        <v>207</v>
       </c>
       <c r="P127" t="inlineStr"/>
       <c r="Q127" t="inlineStr">
@@ -11420,7 +11416,7 @@
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Conshohocken/361-Spring-Garden-Ln-19428/home/38194968</t>
+          <t>https://www.redfin.com/PA/East-Norriton/529-Faith-Dr-19403/home/38324099</t>
         </is>
       </c>
       <c r="S127" t="inlineStr">
@@ -11430,7 +11426,7 @@
       </c>
       <c r="T127" t="inlineStr">
         <is>
-          <t>PAMC2186018</t>
+          <t>PAMC2187382</t>
         </is>
       </c>
       <c r="U127" t="n">
@@ -11448,17 +11444,17 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Lot 14 Kennedy Way</t>
+          <t>361 Spring Garden St</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Warminster Township</t>
+          <t>Conshohocken</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -11467,36 +11463,38 @@
         </is>
       </c>
       <c r="F128" t="n">
-        <v>18974</v>
+        <v>19428</v>
       </c>
       <c r="G128" t="n">
         <v>599900</v>
       </c>
       <c r="H128" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I128" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>THE WOODS AT MEETINGHOUSE</t>
+          <t>MERION HILL</t>
         </is>
       </c>
       <c r="K128" t="n">
-        <v>2800</v>
-      </c>
-      <c r="L128" t="inlineStr"/>
-      <c r="M128" t="inlineStr"/>
+        <v>2650</v>
+      </c>
+      <c r="L128" t="n">
+        <v>23958</v>
+      </c>
+      <c r="M128" t="n">
+        <v>1956</v>
+      </c>
       <c r="N128" t="n">
-        <v>11</v>
+        <v>62</v>
       </c>
       <c r="O128" t="n">
-        <v>214</v>
-      </c>
-      <c r="P128" t="n">
-        <v>225</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="P128" t="inlineStr"/>
       <c r="Q128" t="inlineStr">
         <is>
           <t>Active</t>
@@ -11504,7 +11502,7 @@
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Warminster-Township/Lot-14-Kennedy-WAY-18974/home/204686468</t>
+          <t>https://www.redfin.com/PA/Conshohocken/361-Spring-Garden-Ln-19428/home/38194968</t>
         </is>
       </c>
       <c r="S128" t="inlineStr">
@@ -11514,7 +11512,7 @@
       </c>
       <c r="T128" t="inlineStr">
         <is>
-          <t>PABU2129486</t>
+          <t>PAMC2186018</t>
         </is>
       </c>
       <c r="U128" t="n">
@@ -11532,17 +11530,17 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Single Family Residential</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>770 Almshouse Rd</t>
+          <t>Lot 14 Kennedy Way</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Doylestown</t>
+          <t>Warminster Township</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -11551,7 +11549,7 @@
         </is>
       </c>
       <c r="F129" t="n">
-        <v>18901</v>
+        <v>18974</v>
       </c>
       <c r="G129" t="n">
         <v>599900</v>
@@ -11560,29 +11558,27 @@
         <v>3</v>
       </c>
       <c r="I129" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>Doylestown</t>
+          <t>THE WOODS AT MEETINGHOUSE</t>
         </is>
       </c>
       <c r="K129" t="n">
-        <v>2447</v>
-      </c>
-      <c r="L129" t="n">
-        <v>51575</v>
-      </c>
-      <c r="M129" t="n">
-        <v>1959</v>
-      </c>
+        <v>2800</v>
+      </c>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr"/>
       <c r="N129" t="n">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="O129" t="n">
-        <v>245</v>
-      </c>
-      <c r="P129" t="inlineStr"/>
+        <v>214</v>
+      </c>
+      <c r="P129" t="n">
+        <v>225</v>
+      </c>
       <c r="Q129" t="inlineStr">
         <is>
           <t>Active</t>
@@ -11590,7 +11586,7 @@
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Doylestown/770-Almshouse-Rd-18901/home/38584673</t>
+          <t>https://www.redfin.com/PA/Warminster-Township/Lot-14-Kennedy-WAY-18974/home/204686468</t>
         </is>
       </c>
       <c r="S129" t="inlineStr">
@@ -11600,7 +11596,7 @@
       </c>
       <c r="T129" t="inlineStr">
         <is>
-          <t>PABU2127142</t>
+          <t>PABU2129486</t>
         </is>
       </c>
       <c r="U129" t="n">
@@ -11618,17 +11614,17 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>108A Dock St</t>
+          <t>770 Almshouse Rd</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Bensalem</t>
+          <t>Doylestown</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -11637,7 +11633,7 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>19020</v>
+        <v>18901</v>
       </c>
       <c r="G130" t="n">
         <v>599900</v>
@@ -11646,29 +11642,29 @@
         <v>3</v>
       </c>
       <c r="I130" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>WATERSIDE</t>
+          <t>Doylestown</t>
         </is>
       </c>
       <c r="K130" t="n">
-        <v>2310</v>
-      </c>
-      <c r="L130" t="inlineStr"/>
+        <v>2447</v>
+      </c>
+      <c r="L130" t="n">
+        <v>51575</v>
+      </c>
       <c r="M130" t="n">
-        <v>2017</v>
+        <v>1959</v>
       </c>
       <c r="N130" t="n">
         <v>34</v>
       </c>
       <c r="O130" t="n">
-        <v>260</v>
-      </c>
-      <c r="P130" t="n">
-        <v>265</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="P130" t="inlineStr"/>
       <c r="Q130" t="inlineStr">
         <is>
           <t>Active</t>
@@ -11676,7 +11672,7 @@
       </c>
       <c r="R130" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Bensalem/108A-Dock-St-19020/home/202473066</t>
+          <t>https://www.redfin.com/PA/Doylestown/770-Almshouse-Rd-18901/home/38584673</t>
         </is>
       </c>
       <c r="S130" t="inlineStr">
@@ -11686,7 +11682,7 @@
       </c>
       <c r="T130" t="inlineStr">
         <is>
-          <t>PABU2127682</t>
+          <t>PABU2127142</t>
         </is>
       </c>
       <c r="U130" t="n">
@@ -11704,12 +11700,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Single Family Residential</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>744 Kleckner Rd</t>
+          <t>108A Dock St</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -11729,32 +11725,32 @@
         <v>599900</v>
       </c>
       <c r="H131" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I131" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>GLEN ASHTON FARMS</t>
+          <t>WATERSIDE</t>
         </is>
       </c>
       <c r="K131" t="n">
-        <v>2130</v>
-      </c>
-      <c r="L131" t="n">
-        <v>20300</v>
-      </c>
+        <v>2310</v>
+      </c>
+      <c r="L131" t="inlineStr"/>
       <c r="M131" t="n">
-        <v>1965</v>
+        <v>2017</v>
       </c>
       <c r="N131" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="O131" t="n">
-        <v>282</v>
-      </c>
-      <c r="P131" t="inlineStr"/>
+        <v>260</v>
+      </c>
+      <c r="P131" t="n">
+        <v>265</v>
+      </c>
       <c r="Q131" t="inlineStr">
         <is>
           <t>Active</t>
@@ -11762,7 +11758,7 @@
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Bensalem/744-Kleckner-Rd-19020/home/38417088</t>
+          <t>https://www.redfin.com/PA/Bensalem/108A-Dock-St-19020/home/202473066</t>
         </is>
       </c>
       <c r="S131" t="inlineStr">
@@ -11772,7 +11768,7 @@
       </c>
       <c r="T131" t="inlineStr">
         <is>
-          <t>PABU2126214</t>
+          <t>PABU2127682</t>
         </is>
       </c>
       <c r="U131" t="n">
@@ -11795,7 +11791,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>3007 Rampart Rd</t>
+          <t>744 Kleckner Rd</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -11818,27 +11814,27 @@
         <v>4</v>
       </c>
       <c r="I132" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>SPRINGDALE</t>
+          <t>GLEN ASHTON FARMS</t>
         </is>
       </c>
       <c r="K132" t="n">
-        <v>2504</v>
+        <v>2130</v>
       </c>
       <c r="L132" t="n">
-        <v>12600</v>
+        <v>20300</v>
       </c>
       <c r="M132" t="n">
-        <v>1985</v>
+        <v>1965</v>
       </c>
       <c r="N132" t="n">
-        <v>83</v>
+        <v>41</v>
       </c>
       <c r="O132" t="n">
-        <v>240</v>
+        <v>282</v>
       </c>
       <c r="P132" t="inlineStr"/>
       <c r="Q132" t="inlineStr">
@@ -11848,7 +11844,7 @@
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Bensalem/3007-Rampart-Rd-19020/home/38397038</t>
+          <t>https://www.redfin.com/PA/Bensalem/744-Kleckner-Rd-19020/home/38417088</t>
         </is>
       </c>
       <c r="S132" t="inlineStr">
@@ -11858,7 +11854,7 @@
       </c>
       <c r="T132" t="inlineStr">
         <is>
-          <t>PABU2123304</t>
+          <t>PABU2126214</t>
         </is>
       </c>
       <c r="U132" t="n">
@@ -11881,7 +11877,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2623 Knights Rd</t>
+          <t>3007 Rampart Rd</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -11901,30 +11897,30 @@
         <v>599900</v>
       </c>
       <c r="H133" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I133" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>EDDINGTON GDNS</t>
+          <t>SPRINGDALE</t>
         </is>
       </c>
       <c r="K133" t="n">
-        <v>3060</v>
+        <v>2504</v>
       </c>
       <c r="L133" t="n">
-        <v>9690</v>
+        <v>12600</v>
       </c>
       <c r="M133" t="n">
-        <v>1988</v>
+        <v>1985</v>
       </c>
       <c r="N133" t="n">
-        <v>256</v>
+        <v>84</v>
       </c>
       <c r="O133" t="n">
-        <v>196</v>
+        <v>240</v>
       </c>
       <c r="P133" t="inlineStr"/>
       <c r="Q133" t="inlineStr">
@@ -11934,7 +11930,7 @@
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Bensalem/2623-Knights-Rd-19020/home/38388577</t>
+          <t>https://www.redfin.com/PA/Bensalem/3007-Rampart-Rd-19020/home/38397038</t>
         </is>
       </c>
       <c r="S133" t="inlineStr">
@@ -11944,7 +11940,7 @@
       </c>
       <c r="T133" t="inlineStr">
         <is>
-          <t>PABU2111334</t>
+          <t>PABU2123304</t>
         </is>
       </c>
       <c r="U133" t="n">
@@ -11962,17 +11958,17 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>326 Silo Mill Ln</t>
+          <t>2623 Knights Rd</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Lansdale</t>
+          <t>Bensalem</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -11981,40 +11977,38 @@
         </is>
       </c>
       <c r="F134" t="n">
-        <v>19446</v>
+        <v>19020</v>
       </c>
       <c r="G134" t="n">
-        <v>599999</v>
+        <v>599900</v>
       </c>
       <c r="H134" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I134" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>CENTER POINT FARM</t>
+          <t>EDDINGTON GDNS</t>
         </is>
       </c>
       <c r="K134" t="n">
-        <v>3721</v>
+        <v>3060</v>
       </c>
       <c r="L134" t="n">
-        <v>3276</v>
+        <v>9690</v>
       </c>
       <c r="M134" t="n">
-        <v>1999</v>
+        <v>1988</v>
       </c>
       <c r="N134" t="n">
-        <v>47</v>
+        <v>257</v>
       </c>
       <c r="O134" t="n">
-        <v>161</v>
-      </c>
-      <c r="P134" t="n">
-        <v>350</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="P134" t="inlineStr"/>
       <c r="Q134" t="inlineStr">
         <is>
           <t>Active</t>
@@ -12022,7 +12016,7 @@
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Lansdale/326-Silo-Mill-Ln-19446/home/39128866</t>
+          <t>https://www.redfin.com/PA/Bensalem/2623-Knights-Rd-19020/home/38388577</t>
         </is>
       </c>
       <c r="S134" t="inlineStr">
@@ -12032,11 +12026,11 @@
       </c>
       <c r="T134" t="inlineStr">
         <is>
-          <t>PAMC2187720</t>
+          <t>PABU2111334</t>
         </is>
       </c>
       <c r="U134" t="n">
-        <v>599999</v>
+        <v>599900</v>
       </c>
       <c r="V134" t="n">
         <v>0</v>
@@ -12055,12 +12049,12 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>242 Hillstone Cir</t>
+          <t>326 Silo Mill Ln</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Souderton</t>
+          <t>Lansdale</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -12069,39 +12063,39 @@
         </is>
       </c>
       <c r="F135" t="n">
-        <v>18964</v>
+        <v>19446</v>
       </c>
       <c r="G135" t="n">
-        <v>600000</v>
+        <v>599999</v>
       </c>
       <c r="H135" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I135" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>HILLSTONE PLANNED COMMUNITY</t>
+          <t>CENTER POINT FARM</t>
         </is>
       </c>
       <c r="K135" t="n">
-        <v>2180</v>
+        <v>3721</v>
       </c>
       <c r="L135" t="n">
-        <v>2178</v>
+        <v>3276</v>
       </c>
       <c r="M135" t="n">
-        <v>2020</v>
+        <v>1999</v>
       </c>
       <c r="N135" t="n">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="O135" t="n">
-        <v>275</v>
+        <v>161</v>
       </c>
       <c r="P135" t="n">
-        <v>172</v>
+        <v>350</v>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
@@ -12110,7 +12104,7 @@
       </c>
       <c r="R135" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Souderton/242-Hillstone-Cir-18964/home/170666734</t>
+          <t>https://www.redfin.com/PA/Lansdale/326-Silo-Mill-Ln-19446/home/39128866</t>
         </is>
       </c>
       <c r="S135" t="inlineStr">
@@ -12120,11 +12114,11 @@
       </c>
       <c r="T135" t="inlineStr">
         <is>
-          <t>PAMC2191376</t>
+          <t>PAMC2187720</t>
         </is>
       </c>
       <c r="U135" t="n">
-        <v>600000</v>
+        <v>599999</v>
       </c>
       <c r="V135" t="n">
         <v>0</v>
@@ -12138,17 +12132,17 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Single Family Residential</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>171 Gulph Hills Rd</t>
+          <t>242 Hillstone Cir</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Radnor</t>
+          <t>Souderton</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -12157,56 +12151,144 @@
         </is>
       </c>
       <c r="F136" t="n">
-        <v>19087</v>
-      </c>
-      <c r="G136" t="inlineStr"/>
+        <v>18964</v>
+      </c>
+      <c r="G136" t="n">
+        <v>600000</v>
+      </c>
       <c r="H136" t="n">
         <v>3</v>
       </c>
       <c r="I136" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>HILLSTONE PLANNED COMMUNITY</t>
+        </is>
+      </c>
+      <c r="K136" t="n">
+        <v>2180</v>
+      </c>
+      <c r="L136" t="n">
+        <v>2178</v>
+      </c>
+      <c r="M136" t="n">
+        <v>2020</v>
+      </c>
+      <c r="N136" t="n">
+        <v>8</v>
+      </c>
+      <c r="O136" t="n">
+        <v>275</v>
+      </c>
+      <c r="P136" t="n">
+        <v>172</v>
+      </c>
+      <c r="Q136" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="R136" t="inlineStr">
+        <is>
+          <t>https://www.redfin.com/PA/Souderton/242-Hillstone-Cir-18964/home/170666734</t>
+        </is>
+      </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>BRIGHT MLS</t>
+        </is>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>PAMC2191376</t>
+        </is>
+      </c>
+      <c r="U136" t="n">
+        <v>600000</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>MLS Listing</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Single Family Residential</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>171 Gulph Hills Rd</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Radnor</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="F137" t="n">
+        <v>19087</v>
+      </c>
+      <c r="G137" t="inlineStr"/>
+      <c r="H137" t="n">
         <v>3</v>
       </c>
-      <c r="J136" t="inlineStr">
+      <c r="I137" t="n">
+        <v>3</v>
+      </c>
+      <c r="J137" t="inlineStr">
         <is>
           <t>Wayne</t>
         </is>
       </c>
-      <c r="K136" t="n">
+      <c r="K137" t="n">
         <v>3480</v>
       </c>
-      <c r="L136" t="inlineStr"/>
-      <c r="M136" t="n">
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="n">
         <v>1965</v>
       </c>
-      <c r="N136" t="n">
-        <v>11</v>
-      </c>
-      <c r="O136" t="inlineStr"/>
-      <c r="P136" t="inlineStr"/>
-      <c r="Q136" t="inlineStr">
+      <c r="N137" t="n">
+        <v>12</v>
+      </c>
+      <c r="O137" t="inlineStr"/>
+      <c r="P137" t="inlineStr"/>
+      <c r="Q137" t="inlineStr">
         <is>
           <t>Pre On-Market</t>
         </is>
       </c>
-      <c r="R136" t="inlineStr">
+      <c r="R137" t="inlineStr">
         <is>
           <t>https://www.redfin.com/PA/Radnor/171-Gulph-Hills-Rd-19087/home/38970453</t>
         </is>
       </c>
-      <c r="S136" t="inlineStr">
+      <c r="S137" t="inlineStr">
         <is>
           <t>Compass International Holdings</t>
         </is>
       </c>
-      <c r="T136" t="inlineStr">
+      <c r="T137" t="inlineStr">
         <is>
           <t>2177219236041842105</t>
         </is>
       </c>
-      <c r="U136" t="n">
-        <v>0</v>
-      </c>
-      <c r="V136" t="n">
+      <c r="U137" t="n">
+        <v>0</v>
+      </c>
+      <c r="V137" t="n">
         <v>0</v>
       </c>
     </row>

--- a/homes.xlsx
+++ b/homes.xlsx
@@ -661,7 +661,7 @@
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
@@ -737,7 +737,7 @@
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
@@ -989,7 +989,7 @@
         <v>1910</v>
       </c>
       <c r="N7" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="O7" t="n">
         <v>87</v>
@@ -1247,7 +1247,7 @@
         <v>1892</v>
       </c>
       <c r="N10" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O10" t="n">
         <v>95</v>
@@ -1419,7 +1419,7 @@
         <v>1900</v>
       </c>
       <c r="N12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O12" t="n">
         <v>67</v>
@@ -1505,7 +1505,7 @@
         <v>1900</v>
       </c>
       <c r="N13" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O13" t="n">
         <v>119</v>
@@ -1591,7 +1591,7 @@
         <v>1923</v>
       </c>
       <c r="N14" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O14" t="n">
         <v>87</v>
@@ -1677,7 +1677,7 @@
         <v>1895</v>
       </c>
       <c r="N15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O15" t="n">
         <v>116</v>
@@ -1763,7 +1763,7 @@
         <v>1900</v>
       </c>
       <c r="N16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O16" t="n">
         <v>86</v>
@@ -2103,7 +2103,7 @@
         <v>1900</v>
       </c>
       <c r="N20" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="O20" t="n">
         <v>123</v>
@@ -2439,7 +2439,7 @@
         <v>2001</v>
       </c>
       <c r="N24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O24" t="n">
         <v>121</v>
@@ -2699,7 +2699,7 @@
         <v>1870</v>
       </c>
       <c r="N27" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O27" t="n">
         <v>126</v>
@@ -2785,7 +2785,7 @@
         <v>1910</v>
       </c>
       <c r="N28" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="O28" t="n">
         <v>134</v>
@@ -2869,7 +2869,7 @@
         <v>2003</v>
       </c>
       <c r="N29" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="O29" t="n">
         <v>142</v>
@@ -2955,7 +2955,7 @@
         <v>1900</v>
       </c>
       <c r="N30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O30" t="n">
         <v>128</v>
@@ -3039,7 +3039,7 @@
         <v>1920</v>
       </c>
       <c r="N31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O31" t="n">
         <v>111</v>
@@ -3383,7 +3383,7 @@
         <v>1920</v>
       </c>
       <c r="N35" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O35" t="n">
         <v>103</v>
@@ -3897,7 +3897,7 @@
         <v>1900</v>
       </c>
       <c r="N41" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O41" t="n">
         <v>163</v>
@@ -3983,7 +3983,7 @@
         <v>1907</v>
       </c>
       <c r="N42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O42" t="n">
         <v>143</v>
@@ -4069,7 +4069,7 @@
         <v>1920</v>
       </c>
       <c r="N43" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O43" t="n">
         <v>131</v>
@@ -4155,7 +4155,7 @@
         <v>1875</v>
       </c>
       <c r="N44" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O44" t="n">
         <v>144</v>
@@ -4241,7 +4241,7 @@
         <v>1901</v>
       </c>
       <c r="N45" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O45" t="n">
         <v>146</v>
@@ -4499,7 +4499,7 @@
         <v>1908</v>
       </c>
       <c r="N48" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr"/>
@@ -4669,7 +4669,7 @@
         <v>1900</v>
       </c>
       <c r="N50" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O50" t="n">
         <v>144</v>
@@ -4841,7 +4841,7 @@
         <v>1895</v>
       </c>
       <c r="N52" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O52" t="n">
         <v>148</v>
@@ -4927,7 +4927,7 @@
         <v>1985</v>
       </c>
       <c r="N53" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="O53" t="n">
         <v>177</v>
@@ -5015,7 +5015,7 @@
         <v>1850</v>
       </c>
       <c r="N54" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O54" t="n">
         <v>160</v>
@@ -5273,7 +5273,7 @@
         <v>1910</v>
       </c>
       <c r="N57" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="O57" t="n">
         <v>177</v>
@@ -5531,7 +5531,7 @@
         <v>1885</v>
       </c>
       <c r="N60" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O60" t="n">
         <v>124</v>
@@ -5703,7 +5703,7 @@
         <v>1910</v>
       </c>
       <c r="N62" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O62" t="n">
         <v>162</v>
@@ -5961,7 +5961,7 @@
         <v>1900</v>
       </c>
       <c r="N65" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O65" t="n">
         <v>124</v>
@@ -6047,7 +6047,7 @@
         <v>1940</v>
       </c>
       <c r="N66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O66" t="n">
         <v>187</v>
@@ -6133,7 +6133,7 @@
         <v>1900</v>
       </c>
       <c r="N67" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O67" t="n">
         <v>150</v>
@@ -6219,7 +6219,7 @@
         <v>1982</v>
       </c>
       <c r="N68" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O68" t="n">
         <v>198</v>
@@ -6305,7 +6305,7 @@
         <v>2026</v>
       </c>
       <c r="N69" t="n">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O69" t="n">
         <v>171</v>
@@ -6557,7 +6557,7 @@
         <v>1925</v>
       </c>
       <c r="N72" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O72" t="n">
         <v>149</v>
@@ -7157,7 +7157,7 @@
         <v>2011</v>
       </c>
       <c r="N79" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O79" t="n">
         <v>203</v>
@@ -7327,7 +7327,7 @@
         <v>1933</v>
       </c>
       <c r="N81" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O81" t="n">
         <v>201</v>
@@ -7413,7 +7413,7 @@
         <v>2017</v>
       </c>
       <c r="N82" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O82" t="n">
         <v>166</v>
@@ -7501,7 +7501,7 @@
         <v>1924</v>
       </c>
       <c r="N83" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O83" t="n">
         <v>155</v>
@@ -7587,7 +7587,7 @@
         <v>1900</v>
       </c>
       <c r="N84" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="O84" t="n">
         <v>138</v>
@@ -8017,7 +8017,7 @@
         <v>1919</v>
       </c>
       <c r="N89" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O89" t="n">
         <v>148</v>
@@ -8103,7 +8103,7 @@
         <v>1890</v>
       </c>
       <c r="N90" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O90" t="n">
         <v>151</v>
@@ -8189,7 +8189,7 @@
         <v>1900</v>
       </c>
       <c r="N91" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O91" t="n">
         <v>162</v>
@@ -8359,7 +8359,7 @@
         <v>1977</v>
       </c>
       <c r="N93" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="O93" t="n">
         <v>181</v>
@@ -8447,7 +8447,7 @@
         <v>1899</v>
       </c>
       <c r="N94" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O94" t="n">
         <v>205</v>
@@ -8533,7 +8533,7 @@
         <v>1977</v>
       </c>
       <c r="N95" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="O95" t="n">
         <v>181</v>
@@ -8707,7 +8707,7 @@
         <v>1974</v>
       </c>
       <c r="N97" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O97" t="n">
         <v>189</v>
@@ -9053,7 +9053,7 @@
         <v>1899</v>
       </c>
       <c r="N101" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O101" t="n">
         <v>208</v>
@@ -9311,7 +9311,7 @@
         <v>1965</v>
       </c>
       <c r="N104" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O104" t="n">
         <v>228</v>
@@ -9397,7 +9397,7 @@
         <v>2015</v>
       </c>
       <c r="N105" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O105" t="n">
         <v>183</v>
@@ -9655,7 +9655,7 @@
         <v>1928</v>
       </c>
       <c r="N108" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O108" t="n">
         <v>226</v>
@@ -9913,7 +9913,7 @@
         <v>1965</v>
       </c>
       <c r="N111" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O111" t="n">
         <v>213</v>
@@ -9999,7 +9999,7 @@
         <v>1986</v>
       </c>
       <c r="N112" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O112" t="n">
         <v>230</v>
@@ -10087,7 +10087,7 @@
         <v>1900</v>
       </c>
       <c r="N113" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O113" t="n">
         <v>159</v>
@@ -10173,7 +10173,7 @@
         <v>1935</v>
       </c>
       <c r="N114" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O114" t="n">
         <v>188</v>
@@ -10259,7 +10259,7 @@
         <v>2015</v>
       </c>
       <c r="N115" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O115" t="n">
         <v>199</v>
@@ -10347,7 +10347,7 @@
         <v>1900</v>
       </c>
       <c r="N116" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O116" t="n">
         <v>191</v>
@@ -10693,7 +10693,7 @@
         <v>2005</v>
       </c>
       <c r="N120" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O120" t="n">
         <v>207</v>
@@ -11043,7 +11043,7 @@
         <v>1900</v>
       </c>
       <c r="N124" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O124" t="n">
         <v>102</v>
@@ -11737,7 +11737,7 @@
         <v>1978</v>
       </c>
       <c r="N132" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="O132" t="n">
         <v>237</v>
@@ -11823,7 +11823,7 @@
         <v>1925</v>
       </c>
       <c r="N133" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O133" t="n">
         <v>234</v>
@@ -11907,7 +11907,7 @@
         <v>1900</v>
       </c>
       <c r="N134" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O134" t="n">
         <v>163</v>
@@ -12167,7 +12167,7 @@
         <v>1974</v>
       </c>
       <c r="N137" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O137" t="n">
         <v>220</v>
@@ -12177,7 +12177,7 @@
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>Pre On-Market</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="R137" t="inlineStr">
@@ -12505,7 +12505,7 @@
         <v>1890</v>
       </c>
       <c r="N141" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O141" t="n">
         <v>162</v>
@@ -12589,7 +12589,7 @@
         <v>1880</v>
       </c>
       <c r="N142" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O142" t="n">
         <v>145</v>
@@ -12937,7 +12937,7 @@
         <v>1976</v>
       </c>
       <c r="N146" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O146" t="n">
         <v>212</v>
@@ -13101,7 +13101,7 @@
         <v>1959</v>
       </c>
       <c r="N148" t="n">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O148" t="n">
         <v>184</v>
@@ -13187,7 +13187,7 @@
         <v>2006</v>
       </c>
       <c r="N149" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O149" t="n">
         <v>199</v>
@@ -13445,7 +13445,7 @@
         <v>1989</v>
       </c>
       <c r="N152" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O152" t="n">
         <v>226</v>
@@ -13879,7 +13879,7 @@
         <v>1957</v>
       </c>
       <c r="N157" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O157" t="n">
         <v>212</v>
@@ -14139,7 +14139,7 @@
         <v>1925</v>
       </c>
       <c r="N160" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O160" t="n">
         <v>201</v>
@@ -14399,7 +14399,7 @@
         <v>1950</v>
       </c>
       <c r="N163" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="O163" t="n">
         <v>237</v>
@@ -14573,7 +14573,7 @@
         <v>1980</v>
       </c>
       <c r="N165" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O165" t="n">
         <v>203</v>
@@ -14657,7 +14657,7 @@
         <v>1899</v>
       </c>
       <c r="N166" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O166" t="n">
         <v>140</v>
@@ -14743,7 +14743,7 @@
         <v>1967</v>
       </c>
       <c r="N167" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O167" t="n">
         <v>242</v>
@@ -15351,7 +15351,7 @@
         <v>1885</v>
       </c>
       <c r="N174" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O174" t="n">
         <v>198</v>
@@ -15695,7 +15695,7 @@
         <v>1857</v>
       </c>
       <c r="N178" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O178" t="n">
         <v>205</v>
@@ -15781,7 +15781,7 @@
         <v>1974</v>
       </c>
       <c r="N179" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O179" t="n">
         <v>207</v>
@@ -15867,7 +15867,7 @@
         <v>1950</v>
       </c>
       <c r="N180" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="O180" t="n">
         <v>241</v>
@@ -16383,7 +16383,7 @@
         <v>2022</v>
       </c>
       <c r="N186" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O186" t="n">
         <v>259</v>
@@ -16557,7 +16557,7 @@
         <v>1930</v>
       </c>
       <c r="N188" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O188" t="n">
         <v>253</v>
@@ -16643,7 +16643,7 @@
         <v>2023</v>
       </c>
       <c r="N189" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O189" t="n">
         <v>259</v>
@@ -16731,7 +16731,7 @@
         <v>1976</v>
       </c>
       <c r="N190" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O190" t="n">
         <v>248</v>
@@ -17169,7 +17169,7 @@
         <v>1900</v>
       </c>
       <c r="N195" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="O195" t="n">
         <v>119</v>
@@ -17341,7 +17341,7 @@
         <v>1983</v>
       </c>
       <c r="N197" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O197" t="n">
         <v>263</v>
@@ -17517,7 +17517,7 @@
         <v>1972</v>
       </c>
       <c r="N199" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O199" t="n">
         <v>197</v>
@@ -18031,7 +18031,7 @@
         <v>1998</v>
       </c>
       <c r="N205" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O205" t="n">
         <v>253</v>
@@ -18119,7 +18119,7 @@
         <v>1961</v>
       </c>
       <c r="N206" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O206" t="n">
         <v>208</v>
@@ -18205,7 +18205,7 @@
         <v>1985</v>
       </c>
       <c r="N207" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O207" t="n">
         <v>271</v>
@@ -18901,7 +18901,7 @@
         <v>1976</v>
       </c>
       <c r="N215" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O215" t="n">
         <v>234</v>
@@ -19073,7 +19073,7 @@
         <v>1982</v>
       </c>
       <c r="N217" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O217" t="n">
         <v>241</v>
@@ -19247,7 +19247,7 @@
         <v>2026</v>
       </c>
       <c r="N219" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O219" t="n">
         <v>219</v>
@@ -19333,7 +19333,7 @@
         <v>2026</v>
       </c>
       <c r="N220" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O220" t="n">
         <v>219</v>
@@ -19419,7 +19419,7 @@
         <v>1931</v>
       </c>
       <c r="N221" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O221" t="n">
         <v>190</v>
@@ -19757,7 +19757,7 @@
         <v>2003</v>
       </c>
       <c r="N225" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O225" t="n">
         <v>266</v>
@@ -19929,7 +19929,7 @@
         <v>1930</v>
       </c>
       <c r="N227" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O227" t="n">
         <v>179</v>
@@ -20273,7 +20273,7 @@
         <v>1910</v>
       </c>
       <c r="N231" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O231" t="n">
         <v>238</v>
@@ -20709,7 +20709,7 @@
         <v>1920</v>
       </c>
       <c r="N236" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O236" t="n">
         <v>239</v>
@@ -21053,7 +21053,7 @@
         <v>1900</v>
       </c>
       <c r="N240" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O240" t="n">
         <v>146</v>
@@ -21483,7 +21483,7 @@
         <v>1998</v>
       </c>
       <c r="N245" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O245" t="n">
         <v>198</v>
@@ -21571,7 +21571,7 @@
         <v>1995</v>
       </c>
       <c r="N246" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O246" t="n">
         <v>212</v>
@@ -21745,7 +21745,7 @@
         <v>1960</v>
       </c>
       <c r="N248" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O248" t="n">
         <v>258</v>
@@ -22349,7 +22349,7 @@
         <v>1957</v>
       </c>
       <c r="N255" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O255" t="n">
         <v>267</v>
@@ -22435,7 +22435,7 @@
         <v>1935</v>
       </c>
       <c r="N256" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O256" t="n">
         <v>294</v>
@@ -22695,7 +22695,7 @@
         <v>1957</v>
       </c>
       <c r="N259" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O259" t="n">
         <v>294</v>
@@ -22781,7 +22781,7 @@
         <v>1973</v>
       </c>
       <c r="N260" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O260" t="n">
         <v>243</v>
@@ -23041,7 +23041,7 @@
         <v>1927</v>
       </c>
       <c r="N263" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O263" t="n">
         <v>120</v>
@@ -23213,7 +23213,7 @@
       </c>
       <c r="M265" t="inlineStr"/>
       <c r="N265" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O265" t="n">
         <v>241</v>
@@ -23301,7 +23301,7 @@
         <v>2007</v>
       </c>
       <c r="N266" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O266" t="n">
         <v>238</v>
@@ -23387,7 +23387,7 @@
         <v>2026</v>
       </c>
       <c r="N267" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O267" t="n">
         <v>241</v>
@@ -23471,7 +23471,7 @@
         <v>2026</v>
       </c>
       <c r="N268" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O268" t="n">
         <v>241</v>
@@ -23557,7 +23557,7 @@
         <v>1952</v>
       </c>
       <c r="N269" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O269" t="n">
         <v>266</v>
@@ -23905,7 +23905,7 @@
         <v>1830</v>
       </c>
       <c r="N273" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="O273" t="n">
         <v>206</v>
@@ -24163,7 +24163,7 @@
         <v>1949</v>
       </c>
       <c r="N276" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O276" t="n">
         <v>276</v>
@@ -24249,7 +24249,7 @@
         <v>1965</v>
       </c>
       <c r="N277" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O277" t="n">
         <v>208</v>
@@ -24593,7 +24593,7 @@
         <v>1957</v>
       </c>
       <c r="N281" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O281" t="n">
         <v>280</v>
@@ -24853,7 +24853,7 @@
         <v>1996</v>
       </c>
       <c r="N284" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O284" t="n">
         <v>215</v>
@@ -24937,7 +24937,7 @@
         <v>2007</v>
       </c>
       <c r="N285" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="O285" t="n">
         <v>196</v>
@@ -25107,7 +25107,7 @@
       </c>
       <c r="M287" t="inlineStr"/>
       <c r="N287" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="O287" t="n">
         <v>234</v>
@@ -25191,7 +25191,7 @@
       </c>
       <c r="M288" t="inlineStr"/>
       <c r="N288" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="O288" t="n">
         <v>234</v>
@@ -25273,7 +25273,7 @@
       <c r="L289" t="inlineStr"/>
       <c r="M289" t="inlineStr"/>
       <c r="N289" t="n">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="O289" t="n">
         <v>300</v>
@@ -25445,7 +25445,7 @@
         <v>1989</v>
       </c>
       <c r="N291" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O291" t="n">
         <v>216</v>
@@ -25795,7 +25795,7 @@
         <v>2000</v>
       </c>
       <c r="N295" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O295" t="n">
         <v>261</v>
@@ -25883,7 +25883,7 @@
         <v>1930</v>
       </c>
       <c r="N296" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O296" t="n">
         <v>218</v>
@@ -26057,7 +26057,7 @@
         <v>1988</v>
       </c>
       <c r="N298" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O298" t="n">
         <v>225</v>
@@ -26145,7 +26145,7 @@
         <v>1947</v>
       </c>
       <c r="N299" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O299" t="n">
         <v>179</v>
@@ -26317,7 +26317,7 @@
         <v>1959</v>
       </c>
       <c r="N301" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O301" t="n">
         <v>263</v>
@@ -26491,7 +26491,7 @@
         <v>1993</v>
       </c>
       <c r="N303" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O303" t="n">
         <v>243</v>
@@ -26839,7 +26839,7 @@
         <v>1983</v>
       </c>
       <c r="N307" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O307" t="n">
         <v>306</v>
@@ -27015,7 +27015,7 @@
         <v>2023</v>
       </c>
       <c r="N309" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O309" t="n">
         <v>271</v>
@@ -27103,7 +27103,7 @@
         <v>2026</v>
       </c>
       <c r="N310" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="O310" t="n">
         <v>265</v>
@@ -27533,7 +27533,7 @@
         <v>2003</v>
       </c>
       <c r="N315" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="O315" t="n">
         <v>237</v>
@@ -27621,7 +27621,7 @@
         <v>1994</v>
       </c>
       <c r="N316" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O316" t="n">
         <v>299</v>
@@ -27709,7 +27709,7 @@
         <v>1979</v>
       </c>
       <c r="N317" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O317" t="n">
         <v>214</v>
@@ -27795,7 +27795,7 @@
         <v>1999</v>
       </c>
       <c r="N318" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O318" t="n">
         <v>190</v>
@@ -27967,7 +27967,7 @@
         <v>1996</v>
       </c>
       <c r="N320" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O320" t="n">
         <v>263</v>
@@ -28055,7 +28055,7 @@
         <v>2024</v>
       </c>
       <c r="N321" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O321" t="n">
         <v>199</v>
@@ -28317,7 +28317,7 @@
         <v>1952</v>
       </c>
       <c r="N324" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O324" t="n">
         <v>294</v>
@@ -28403,7 +28403,7 @@
         <v>1950</v>
       </c>
       <c r="N325" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O325" t="n">
         <v>274</v>
@@ -28489,7 +28489,7 @@
         <v>1997</v>
       </c>
       <c r="N326" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O326" t="n">
         <v>208</v>
@@ -28663,7 +28663,7 @@
         <v>1998</v>
       </c>
       <c r="N328" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O328" t="n">
         <v>240</v>
@@ -28751,7 +28751,7 @@
         <v>1962</v>
       </c>
       <c r="N329" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O329" t="n">
         <v>179</v>
@@ -28837,7 +28837,7 @@
         <v>2025</v>
       </c>
       <c r="N330" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O330" t="n">
         <v>305</v>
@@ -29011,7 +29011,7 @@
         <v>1999</v>
       </c>
       <c r="N332" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O332" t="n">
         <v>257</v>
@@ -29099,7 +29099,7 @@
         <v>1930</v>
       </c>
       <c r="N333" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O333" t="n">
         <v>205</v>
@@ -29271,7 +29271,7 @@
         <v>1997</v>
       </c>
       <c r="N335" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O335" t="n">
         <v>195</v>
@@ -29531,7 +29531,7 @@
         <v>2026</v>
       </c>
       <c r="N338" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O338" t="n">
         <v>250</v>
@@ -29793,7 +29793,7 @@
         <v>1952</v>
       </c>
       <c r="N341" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O341" t="n">
         <v>244</v>
@@ -29875,7 +29875,7 @@
         <v>1880</v>
       </c>
       <c r="N342" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O342" t="inlineStr"/>
       <c r="P342" t="inlineStr"/>
@@ -29957,7 +29957,7 @@
         <v>2026</v>
       </c>
       <c r="N343" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="O343" t="n">
         <v>252</v>
@@ -30045,7 +30045,7 @@
         <v>1955</v>
       </c>
       <c r="N344" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O344" t="n">
         <v>249</v>
@@ -30217,7 +30217,7 @@
         <v>2000</v>
       </c>
       <c r="N346" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O346" t="n">
         <v>196</v>
@@ -30391,7 +30391,7 @@
         <v>1969</v>
       </c>
       <c r="N348" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O348" t="n">
         <v>214</v>
@@ -30997,7 +30997,7 @@
         <v>2011</v>
       </c>
       <c r="N355" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O355" t="n">
         <v>248</v>
@@ -31085,7 +31085,7 @@
         <v>1949</v>
       </c>
       <c r="N356" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O356" t="n">
         <v>286</v>
@@ -31167,7 +31167,7 @@
       <c r="L357" t="inlineStr"/>
       <c r="M357" t="inlineStr"/>
       <c r="N357" t="n">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="O357" t="n">
         <v>265</v>
@@ -31253,7 +31253,7 @@
         <v>1960</v>
       </c>
       <c r="N358" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O358" t="n">
         <v>309</v>
@@ -31337,7 +31337,7 @@
         <v>1975</v>
       </c>
       <c r="N359" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O359" t="n">
         <v>306</v>
@@ -31513,7 +31513,7 @@
         <v>1998</v>
       </c>
       <c r="N361" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O361" t="n">
         <v>305</v>
@@ -31683,7 +31683,7 @@
         <v>1993</v>
       </c>
       <c r="N363" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O363" t="n">
         <v>231</v>
@@ -31769,7 +31769,7 @@
         <v>1998</v>
       </c>
       <c r="N364" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O364" t="n">
         <v>246</v>
@@ -31857,7 +31857,7 @@
         <v>1949</v>
       </c>
       <c r="N365" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O365" t="n">
         <v>157</v>
@@ -32201,7 +32201,7 @@
         <v>1870</v>
       </c>
       <c r="N369" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="O369" t="n">
         <v>291</v>
@@ -32375,7 +32375,7 @@
         <v>1956</v>
       </c>
       <c r="N371" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O371" t="n">
         <v>253</v>
@@ -32547,7 +32547,7 @@
         <v>1974</v>
       </c>
       <c r="N373" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O373" t="n">
         <v>247</v>
@@ -32889,7 +32889,7 @@
         <v>1987</v>
       </c>
       <c r="N377" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O377" t="n">
         <v>223</v>
@@ -33063,7 +33063,7 @@
         <v>1955</v>
       </c>
       <c r="N379" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O379" t="n">
         <v>233</v>
@@ -33149,7 +33149,7 @@
         <v>1987</v>
       </c>
       <c r="N380" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O380" t="n">
         <v>235</v>
@@ -33237,7 +33237,7 @@
         <v>1956</v>
       </c>
       <c r="N381" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O381" t="n">
         <v>297</v>
@@ -33409,7 +33409,7 @@
         <v>1920</v>
       </c>
       <c r="N383" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O383" t="n">
         <v>321</v>
@@ -33491,7 +33491,7 @@
       <c r="L384" t="inlineStr"/>
       <c r="M384" t="inlineStr"/>
       <c r="N384" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="O384" t="n">
         <v>231</v>
@@ -33575,7 +33575,7 @@
       <c r="L385" t="inlineStr"/>
       <c r="M385" t="inlineStr"/>
       <c r="N385" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="O385" t="n">
         <v>231</v>
@@ -33835,7 +33835,7 @@
         <v>1950</v>
       </c>
       <c r="N388" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O388" t="n">
         <v>208</v>
@@ -33921,7 +33921,7 @@
         <v>1996</v>
       </c>
       <c r="N389" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O389" t="n">
         <v>193</v>
@@ -34353,7 +34353,7 @@
         <v>1968</v>
       </c>
       <c r="N394" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O394" t="n">
         <v>248</v>
@@ -34439,7 +34439,7 @@
         <v>1910</v>
       </c>
       <c r="N395" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O395" t="n">
         <v>103</v>
@@ -34525,7 +34525,7 @@
         <v>1920</v>
       </c>
       <c r="N396" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O396" t="n">
         <v>165</v>
@@ -34783,7 +34783,7 @@
         <v>1959</v>
       </c>
       <c r="N399" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O399" t="n">
         <v>294</v>
@@ -34867,7 +34867,7 @@
         <v>1915</v>
       </c>
       <c r="N400" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O400" t="n">
         <v>322</v>
@@ -35213,7 +35213,7 @@
         <v>1908</v>
       </c>
       <c r="N404" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O404" t="n">
         <v>204</v>
@@ -35297,7 +35297,7 @@
         <v>2026</v>
       </c>
       <c r="N405" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O405" t="n">
         <v>237</v>
@@ -35471,7 +35471,7 @@
         <v>1959</v>
       </c>
       <c r="N407" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O407" t="n">
         <v>310</v>
@@ -35731,7 +35731,7 @@
         <v>1959</v>
       </c>
       <c r="N410" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O410" t="n">
         <v>292</v>
@@ -36079,7 +36079,7 @@
         <v>1920</v>
       </c>
       <c r="N414" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O414" t="n">
         <v>340</v>
@@ -36163,7 +36163,7 @@
         <v>2026</v>
       </c>
       <c r="N415" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O415" t="n">
         <v>240</v>
@@ -36511,7 +36511,7 @@
         <v>2020</v>
       </c>
       <c r="N419" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O419" t="n">
         <v>211</v>
@@ -36775,7 +36775,7 @@
         <v>2003</v>
       </c>
       <c r="N422" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O422" t="n">
         <v>237</v>
@@ -36947,7 +36947,7 @@
       </c>
       <c r="M424" t="inlineStr"/>
       <c r="N424" t="n">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="O424" t="n">
         <v>280</v>
@@ -37033,7 +37033,7 @@
         <v>1955</v>
       </c>
       <c r="N425" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O425" t="n">
         <v>278</v>
@@ -37207,7 +37207,7 @@
         <v>1920</v>
       </c>
       <c r="N427" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O427" t="n">
         <v>194</v>
@@ -37553,7 +37553,7 @@
         <v>1961</v>
       </c>
       <c r="N431" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O431" t="n">
         <v>163</v>
@@ -37639,7 +37639,7 @@
         <v>2023</v>
       </c>
       <c r="N432" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="O432" t="n">
         <v>249</v>
@@ -37725,7 +37725,7 @@
         <v>2019</v>
       </c>
       <c r="N433" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O433" t="n">
         <v>259</v>
@@ -37899,7 +37899,7 @@
         <v>2003</v>
       </c>
       <c r="N435" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O435" t="n">
         <v>266</v>
@@ -37987,7 +37987,7 @@
         <v>2003</v>
       </c>
       <c r="N436" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O436" t="n">
         <v>262</v>
@@ -38421,7 +38421,7 @@
         <v>1995</v>
       </c>
       <c r="N441" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O441" t="n">
         <v>257</v>
@@ -38683,7 +38683,7 @@
         <v>1927</v>
       </c>
       <c r="N444" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O444" t="n">
         <v>273</v>
@@ -38853,7 +38853,7 @@
         <v>2003</v>
       </c>
       <c r="N446" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O446" t="n">
         <v>254</v>
@@ -39027,7 +39027,7 @@
         <v>2026</v>
       </c>
       <c r="N448" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O448" t="n">
         <v>271</v>
@@ -39111,7 +39111,7 @@
       <c r="L449" t="inlineStr"/>
       <c r="M449" t="inlineStr"/>
       <c r="N449" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O449" t="n">
         <v>271</v>
@@ -39199,7 +39199,7 @@
         <v>1973</v>
       </c>
       <c r="N450" t="n">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O450" t="n">
         <v>88</v>
@@ -39281,7 +39281,7 @@
         <v>1929</v>
       </c>
       <c r="N451" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O451" t="inlineStr"/>
       <c r="P451" t="inlineStr"/>
@@ -39713,7 +39713,7 @@
         <v>1990</v>
       </c>
       <c r="N456" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O456" t="n">
         <v>252</v>
@@ -39797,7 +39797,7 @@
       <c r="L457" t="inlineStr"/>
       <c r="M457" t="inlineStr"/>
       <c r="N457" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="O457" t="n">
         <v>225</v>
@@ -39881,7 +39881,7 @@
       <c r="L458" t="inlineStr"/>
       <c r="M458" t="inlineStr"/>
       <c r="N458" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="O458" t="n">
         <v>225</v>
@@ -39967,7 +39967,7 @@
         <v>1900</v>
       </c>
       <c r="N459" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O459" t="n">
         <v>191</v>
@@ -40055,7 +40055,7 @@
         <v>1999</v>
       </c>
       <c r="N460" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O460" t="n">
         <v>234</v>
@@ -40401,7 +40401,7 @@
         <v>2016</v>
       </c>
       <c r="N464" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O464" t="n">
         <v>248</v>
@@ -40489,7 +40489,7 @@
         <v>1966</v>
       </c>
       <c r="N465" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O465" t="n">
         <v>286</v>
@@ -40575,7 +40575,7 @@
         <v>1850</v>
       </c>
       <c r="N466" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O466" t="n">
         <v>208</v>
@@ -40831,7 +40831,7 @@
         <v>2026</v>
       </c>
       <c r="N469" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="O469" t="n">
         <v>321</v>
@@ -40915,7 +40915,7 @@
       <c r="L470" t="inlineStr"/>
       <c r="M470" t="inlineStr"/>
       <c r="N470" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="O470" t="n">
         <v>321</v>
@@ -41001,7 +41001,7 @@
         <v>1858</v>
       </c>
       <c r="N471" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O471" t="n">
         <v>201</v>
@@ -41087,7 +41087,7 @@
         <v>2003</v>
       </c>
       <c r="N472" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O472" t="n">
         <v>258</v>
@@ -41261,7 +41261,7 @@
         <v>1997</v>
       </c>
       <c r="N474" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O474" t="n">
         <v>312</v>
@@ -41437,7 +41437,7 @@
         <v>2024</v>
       </c>
       <c r="N476" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="O476" t="n">
         <v>210</v>
@@ -41521,7 +41521,7 @@
       <c r="L477" t="inlineStr"/>
       <c r="M477" t="inlineStr"/>
       <c r="N477" t="n">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="O477" t="n">
         <v>275</v>
@@ -41609,7 +41609,7 @@
         <v>1965</v>
       </c>
       <c r="N478" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O478" t="n">
         <v>276</v>
@@ -41869,7 +41869,7 @@
         <v>1975</v>
       </c>
       <c r="N481" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O481" t="n">
         <v>281</v>
@@ -41955,7 +41955,7 @@
         <v>1956</v>
       </c>
       <c r="N482" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O482" t="n">
         <v>272</v>
@@ -42041,7 +42041,7 @@
         <v>1889</v>
       </c>
       <c r="N483" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O483" t="n">
         <v>185</v>
@@ -42213,7 +42213,7 @@
         <v>1978</v>
       </c>
       <c r="N485" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O485" t="n">
         <v>320</v>
@@ -42471,7 +42471,7 @@
         <v>1996</v>
       </c>
       <c r="N488" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="O488" t="n">
         <v>269</v>
@@ -42729,7 +42729,7 @@
         <v>2008</v>
       </c>
       <c r="N491" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="O491" t="n">
         <v>292</v>
@@ -42817,7 +42817,7 @@
         <v>1992</v>
       </c>
       <c r="N492" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O492" t="n">
         <v>240</v>
@@ -43077,7 +43077,7 @@
         <v>2026</v>
       </c>
       <c r="N495" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O495" t="n">
         <v>236</v>
@@ -43161,7 +43161,7 @@
       <c r="L496" t="inlineStr"/>
       <c r="M496" t="inlineStr"/>
       <c r="N496" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O496" t="n">
         <v>236</v>
@@ -43333,7 +43333,7 @@
         <v>1979</v>
       </c>
       <c r="N498" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O498" t="n">
         <v>241</v>
@@ -43761,7 +43761,7 @@
         <v>2017</v>
       </c>
       <c r="N503" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O503" t="n">
         <v>261</v>
@@ -43849,7 +43849,7 @@
         <v>1984</v>
       </c>
       <c r="N504" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O504" t="n">
         <v>286</v>
@@ -44279,7 +44279,7 @@
         <v>1961</v>
       </c>
       <c r="N509" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O509" t="n">
         <v>304</v>
@@ -44361,7 +44361,7 @@
       <c r="L510" t="inlineStr"/>
       <c r="M510" t="inlineStr"/>
       <c r="N510" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="O510" t="n">
         <v>293</v>
@@ -44449,7 +44449,7 @@
         <v>1965</v>
       </c>
       <c r="N511" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O511" t="n">
         <v>270</v>
@@ -44617,7 +44617,7 @@
       <c r="L513" t="inlineStr"/>
       <c r="M513" t="inlineStr"/>
       <c r="N513" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="O513" t="n">
         <v>293</v>
@@ -44791,7 +44791,7 @@
         <v>1910</v>
       </c>
       <c r="N515" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O515" t="n">
         <v>161</v>
@@ -45139,7 +45139,7 @@
         <v>2005</v>
       </c>
       <c r="N519" t="n">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="O519" t="n">
         <v>267</v>
@@ -45227,7 +45227,7 @@
         <v>1860</v>
       </c>
       <c r="N520" t="n">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="O520" t="n">
         <v>141</v>
@@ -45315,7 +45315,7 @@
         <v>2025</v>
       </c>
       <c r="N521" t="n">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="O521" t="n">
         <v>267</v>
@@ -45403,7 +45403,7 @@
         <v>2025</v>
       </c>
       <c r="N522" t="n">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="O522" t="n">
         <v>267</v>
@@ -45491,7 +45491,7 @@
         <v>2025</v>
       </c>
       <c r="N523" t="n">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="O523" t="n">
         <v>267</v>
@@ -45665,7 +45665,7 @@
         <v>2023</v>
       </c>
       <c r="N525" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O525" t="n">
         <v>158</v>
@@ -45753,7 +45753,7 @@
         <v>1997</v>
       </c>
       <c r="N526" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="O526" t="n">
         <v>294</v>
@@ -45839,7 +45839,7 @@
         <v>2011</v>
       </c>
       <c r="N527" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O527" t="n">
         <v>246</v>
@@ -46015,7 +46015,7 @@
         <v>2026</v>
       </c>
       <c r="N529" t="n">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="O529" t="n">
         <v>285</v>
@@ -46103,7 +46103,7 @@
         <v>2026</v>
       </c>
       <c r="N530" t="n">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="O530" t="n">
         <v>285</v>
@@ -46451,7 +46451,7 @@
         <v>1987</v>
       </c>
       <c r="N534" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O534" t="n">
         <v>181</v>
@@ -46535,7 +46535,7 @@
         <v>1974</v>
       </c>
       <c r="N535" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O535" t="n">
         <v>288</v>
@@ -46617,7 +46617,7 @@
       <c r="L536" t="inlineStr"/>
       <c r="M536" t="inlineStr"/>
       <c r="N536" t="n">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O536" t="n">
         <v>261</v>
@@ -46701,7 +46701,7 @@
         <v>2003</v>
       </c>
       <c r="N537" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="O537" t="n">
         <v>273</v>
@@ -46875,7 +46875,7 @@
         <v>1960</v>
       </c>
       <c r="N539" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O539" t="n">
         <v>338</v>
@@ -46961,7 +46961,7 @@
         <v>2001</v>
       </c>
       <c r="N540" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O540" t="n">
         <v>220</v>
@@ -47049,7 +47049,7 @@
         <v>1947</v>
       </c>
       <c r="N541" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O541" t="n">
         <v>356</v>
@@ -47135,7 +47135,7 @@
         <v>1956</v>
       </c>
       <c r="N542" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O542" t="n">
         <v>210</v>
@@ -47309,7 +47309,7 @@
         <v>2026</v>
       </c>
       <c r="N544" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O544" t="n">
         <v>224</v>
@@ -47395,7 +47395,7 @@
         <v>2026</v>
       </c>
       <c r="N545" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O545" t="n">
         <v>262</v>
@@ -47477,7 +47477,7 @@
       <c r="L546" t="inlineStr"/>
       <c r="M546" t="inlineStr"/>
       <c r="N546" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="O546" t="n">
         <v>272</v>
@@ -47565,7 +47565,7 @@
         <v>2023</v>
       </c>
       <c r="N547" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O547" t="n">
         <v>282</v>
@@ -47653,7 +47653,7 @@
         <v>1957</v>
       </c>
       <c r="N548" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O548" t="n">
         <v>294</v>
@@ -47739,7 +47739,7 @@
         <v>2025</v>
       </c>
       <c r="N549" t="n">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="O549" t="n">
         <v>271</v>
@@ -47827,7 +47827,7 @@
         <v>2005</v>
       </c>
       <c r="N550" t="n">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="O550" t="n">
         <v>271</v>
@@ -47915,7 +47915,7 @@
         <v>2025</v>
       </c>
       <c r="N551" t="n">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="O551" t="n">
         <v>271</v>
@@ -48001,7 +48001,7 @@
       </c>
       <c r="M552" t="inlineStr"/>
       <c r="N552" t="n">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="O552" t="n">
         <v>271</v>
@@ -48089,7 +48089,7 @@
         <v>2021</v>
       </c>
       <c r="N553" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O553" t="n">
         <v>218</v>
@@ -48351,7 +48351,7 @@
         <v>1979</v>
       </c>
       <c r="N556" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O556" t="n">
         <v>224</v>
@@ -48437,7 +48437,7 @@
         <v>1964</v>
       </c>
       <c r="N557" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O557" t="n">
         <v>288</v>
@@ -48609,7 +48609,7 @@
         <v>1926</v>
       </c>
       <c r="N559" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O559" t="n">
         <v>327</v>
@@ -48695,7 +48695,7 @@
         <v>1961</v>
       </c>
       <c r="N560" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O560" t="n">
         <v>184</v>
@@ -48867,7 +48867,7 @@
         <v>2022</v>
       </c>
       <c r="N562" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O562" t="n">
         <v>366</v>
@@ -49041,7 +49041,7 @@
         <v>1925</v>
       </c>
       <c r="N564" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O564" t="n">
         <v>280</v>
@@ -49215,7 +49215,7 @@
         <v>1986</v>
       </c>
       <c r="N566" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O566" t="n">
         <v>274</v>
@@ -49301,7 +49301,7 @@
         <v>2021</v>
       </c>
       <c r="N567" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O567" t="n">
         <v>159</v>
@@ -49475,7 +49475,7 @@
         <v>1920</v>
       </c>
       <c r="N569" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O569" t="n">
         <v>330</v>
@@ -49645,7 +49645,7 @@
         <v>2026</v>
       </c>
       <c r="N571" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O571" t="inlineStr"/>
       <c r="P571" t="inlineStr"/>
@@ -49811,7 +49811,7 @@
       <c r="L573" t="inlineStr"/>
       <c r="M573" t="inlineStr"/>
       <c r="N573" t="n">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="O573" t="n">
         <v>292</v>
@@ -49899,7 +49899,7 @@
         <v>1990</v>
       </c>
       <c r="N574" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O574" t="n">
         <v>224</v>
@@ -50073,7 +50073,7 @@
         <v>1914</v>
       </c>
       <c r="N576" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O576" t="n">
         <v>319</v>
@@ -50159,7 +50159,7 @@
         <v>1982</v>
       </c>
       <c r="N577" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O577" t="n">
         <v>253</v>
@@ -50245,7 +50245,7 @@
         <v>1967</v>
       </c>
       <c r="N578" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O578" t="n">
         <v>247</v>
@@ -50331,7 +50331,7 @@
         <v>1918</v>
       </c>
       <c r="N579" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O579" t="n">
         <v>316</v>
@@ -50501,7 +50501,7 @@
         <v>2001</v>
       </c>
       <c r="N581" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O581" t="n">
         <v>248</v>
@@ -50843,7 +50843,7 @@
         <v>2026</v>
       </c>
       <c r="N585" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O585" t="n">
         <v>301</v>
@@ -50931,7 +50931,7 @@
         <v>2026</v>
       </c>
       <c r="N586" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O586" t="n">
         <v>270</v>
@@ -51019,7 +51019,7 @@
         <v>2022</v>
       </c>
       <c r="N587" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O587" t="n">
         <v>257</v>
@@ -51107,7 +51107,7 @@
         <v>1969</v>
       </c>
       <c r="N588" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O588" t="n">
         <v>285</v>
@@ -51279,7 +51279,7 @@
         <v>2021</v>
       </c>
       <c r="N590" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O590" t="n">
         <v>216</v>
@@ -51363,7 +51363,7 @@
         <v>1959</v>
       </c>
       <c r="N591" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O591" t="inlineStr"/>
       <c r="P591" t="inlineStr"/>
@@ -51447,7 +51447,7 @@
         <v>2019</v>
       </c>
       <c r="N592" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O592" t="n">
         <v>267</v>
@@ -51535,7 +51535,7 @@
         <v>2022</v>
       </c>
       <c r="N593" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O593" t="n">
         <v>191</v>
@@ -51623,7 +51623,7 @@
         <v>1974</v>
       </c>
       <c r="N594" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O594" t="n">
         <v>340</v>
@@ -51709,7 +51709,7 @@
         <v>1971</v>
       </c>
       <c r="N595" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O595" t="n">
         <v>308</v>
@@ -51881,7 +51881,7 @@
         <v>2026</v>
       </c>
       <c r="N597" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O597" t="n">
         <v>274</v>
@@ -52053,7 +52053,7 @@
       </c>
       <c r="M599" t="inlineStr"/>
       <c r="N599" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O599" t="n">
         <v>271</v>
@@ -52139,7 +52139,7 @@
         <v>2026</v>
       </c>
       <c r="N600" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O600" t="n">
         <v>271</v>
@@ -52223,7 +52223,7 @@
         <v>2026</v>
       </c>
       <c r="N601" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O601" t="n">
         <v>271</v>
@@ -52307,7 +52307,7 @@
         <v>2026</v>
       </c>
       <c r="N602" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O602" t="n">
         <v>271</v>
@@ -52567,7 +52567,7 @@
         <v>1950</v>
       </c>
       <c r="N605" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="O605" t="n">
         <v>200</v>
@@ -52653,7 +52653,7 @@
         <v>1923</v>
       </c>
       <c r="N606" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O606" t="n">
         <v>204</v>
@@ -52739,7 +52739,7 @@
         <v>1955</v>
       </c>
       <c r="N607" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O607" t="n">
         <v>324</v>
@@ -52825,7 +52825,7 @@
         <v>1997</v>
       </c>
       <c r="N608" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O608" t="n">
         <v>221</v>
@@ -52913,7 +52913,7 @@
         <v>1880</v>
       </c>
       <c r="N609" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O609" t="n">
         <v>193</v>
@@ -52999,7 +52999,7 @@
         <v>2026</v>
       </c>
       <c r="N610" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O610" t="n">
         <v>352</v>
@@ -53083,7 +53083,7 @@
         <v>2017</v>
       </c>
       <c r="N611" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O611" t="n">
         <v>260</v>
@@ -53171,7 +53171,7 @@
         <v>1965</v>
       </c>
       <c r="N612" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O612" t="n">
         <v>282</v>
@@ -53257,7 +53257,7 @@
         <v>1985</v>
       </c>
       <c r="N613" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O613" t="n">
         <v>240</v>
@@ -53343,7 +53343,7 @@
         <v>1988</v>
       </c>
       <c r="N614" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O614" t="n">
         <v>196</v>
@@ -53515,7 +53515,7 @@
         <v>2014</v>
       </c>
       <c r="N616" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O616" t="n">
         <v>387</v>
@@ -53601,7 +53601,7 @@
         <v>1986</v>
       </c>
       <c r="N617" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="O617" t="n">
         <v>207</v>
@@ -53945,7 +53945,7 @@
         <v>1957</v>
       </c>
       <c r="N621" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O621" t="n">
         <v>331</v>
@@ -54031,7 +54031,7 @@
         <v>1969</v>
       </c>
       <c r="N622" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O622" t="n">
         <v>324</v>
@@ -54113,7 +54113,7 @@
       <c r="L623" t="inlineStr"/>
       <c r="M623" t="inlineStr"/>
       <c r="N623" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O623" t="n">
         <v>329</v>
@@ -54191,7 +54191,7 @@
         <v>1982</v>
       </c>
       <c r="N624" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O624" t="n">
         <v>273</v>
@@ -54449,7 +54449,7 @@
         <v>1999</v>
       </c>
       <c r="N627" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="O627" t="n">
         <v>161</v>
@@ -54881,7 +54881,7 @@
         <v>2020</v>
       </c>
       <c r="N632" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O632" t="n">
         <v>275</v>
@@ -54967,7 +54967,7 @@
         <v>2026</v>
       </c>
       <c r="N633" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O633" t="inlineStr"/>
       <c r="P633" t="inlineStr"/>
